--- a/research/traditional_assets/database/data/indonesia/indonesia_chemical_diversified.xlsx
+++ b/research/traditional_assets/database/data/indonesia/indonesia_chemical_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1042423532096948</v>
+        <v>0.1040481200326335</v>
       </c>
       <c r="C2">
-        <v>157.0733717797279</v>
+        <v>155.980458030876</v>
       </c>
       <c r="D2">
-        <v>140.0733717797279</v>
+        <v>140.540458030876</v>
       </c>
       <c r="E2">
-        <v>-61.99999999999999</v>
+        <v>-60.43999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="G2">
         <v>17</v>
@@ -1451,28 +1451,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.078468</v>
       </c>
       <c r="N2">
-        <v>25.27777777777778</v>
+        <v>25.19930977777778</v>
       </c>
       <c r="O2">
-        <v>5.561111111111111</v>
+        <v>5.543848151111111</v>
       </c>
       <c r="P2">
-        <v>19.71666666666667</v>
+        <v>19.65546162666667</v>
       </c>
       <c r="Q2">
-        <v>28.21666666666667</v>
+        <v>28.15546162666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1042423532096948</v>
+        <v>0.1047028081137712</v>
       </c>
       <c r="T2">
-        <v>0.8504074490426664</v>
+        <v>0.8571076289442147</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>322.1412267137914</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1040481200326335</v>
+        <v>0.1038538868555721</v>
       </c>
       <c r="C3">
-        <v>155.980458030876</v>
+        <v>154.8906697797793</v>
       </c>
       <c r="D3">
-        <v>140.540458030876</v>
+        <v>141.0106697797793</v>
       </c>
       <c r="E3">
-        <v>-60.43999999999999</v>
+        <v>-58.88</v>
       </c>
       <c r="F3">
-        <v>1.56</v>
+        <v>3.12</v>
       </c>
       <c r="G3">
         <v>17</v>
@@ -1533,28 +1533,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M3">
-        <v>0.078468</v>
+        <v>0.156936</v>
       </c>
       <c r="N3">
-        <v>25.19930977777778</v>
+        <v>25.12084177777778</v>
       </c>
       <c r="O3">
-        <v>5.543848151111111</v>
+        <v>5.526585191111111</v>
       </c>
       <c r="P3">
-        <v>19.65546162666667</v>
+        <v>19.59425658666667</v>
       </c>
       <c r="Q3">
-        <v>28.15546162666667</v>
+        <v>28.09425658666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1047028081137712</v>
+        <v>0.1051726600567063</v>
       </c>
       <c r="T3">
-        <v>0.8571076289442147</v>
+        <v>0.8639445472111007</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>322.1412267137914</v>
+        <v>161.0706133568957</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1038538868555721</v>
+        <v>0.1036596536785108</v>
       </c>
       <c r="C4">
-        <v>154.8906697797793</v>
+        <v>153.8040385030533</v>
       </c>
       <c r="D4">
-        <v>141.0106697797793</v>
+        <v>141.4840385030533</v>
       </c>
       <c r="E4">
-        <v>-58.88</v>
+        <v>-57.31999999999999</v>
       </c>
       <c r="F4">
-        <v>3.12</v>
+        <v>4.68</v>
       </c>
       <c r="G4">
         <v>17</v>
@@ -1615,28 +1615,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M4">
-        <v>0.156936</v>
+        <v>0.235404</v>
       </c>
       <c r="N4">
-        <v>25.12084177777778</v>
+        <v>25.04237377777778</v>
       </c>
       <c r="O4">
-        <v>5.526585191111111</v>
+        <v>5.509322231111112</v>
       </c>
       <c r="P4">
-        <v>19.59425658666667</v>
+        <v>19.53305154666667</v>
       </c>
       <c r="Q4">
-        <v>28.09425658666667</v>
+        <v>28.03305154666667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1051726600567063</v>
+        <v>0.1056521996685678</v>
       </c>
       <c r="T4">
-        <v>0.8639445472111007</v>
+        <v>0.8709224328649328</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>161.0706133568957</v>
+        <v>107.3804089045971</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1036596536785108</v>
+        <v>0.1034654205014495</v>
       </c>
       <c r="C5">
-        <v>153.8040385030533</v>
+        <v>152.7205961014016</v>
       </c>
       <c r="D5">
-        <v>141.4840385030533</v>
+        <v>141.9605961014016</v>
       </c>
       <c r="E5">
-        <v>-57.31999999999999</v>
+        <v>-55.75999999999999</v>
       </c>
       <c r="F5">
-        <v>4.68</v>
+        <v>6.24</v>
       </c>
       <c r="G5">
         <v>17</v>
@@ -1697,28 +1697,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M5">
-        <v>0.235404</v>
+        <v>0.313872</v>
       </c>
       <c r="N5">
-        <v>25.04237377777778</v>
+        <v>24.96390577777778</v>
       </c>
       <c r="O5">
-        <v>5.509322231111112</v>
+        <v>5.492059271111112</v>
       </c>
       <c r="P5">
-        <v>19.53305154666667</v>
+        <v>19.47184650666667</v>
       </c>
       <c r="Q5">
-        <v>28.03305154666667</v>
+        <v>27.97184650666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1056521996685678</v>
+        <v>0.1061417296890099</v>
       </c>
       <c r="T5">
-        <v>0.8709224328649328</v>
+        <v>0.8780456911365531</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>107.3804089045971</v>
+        <v>80.53530667844784</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1034654205014495</v>
+        <v>0.1032711873243882</v>
       </c>
       <c r="C6">
-        <v>152.7205961014016</v>
+        <v>151.6403749067821</v>
       </c>
       <c r="D6">
-        <v>141.9605961014016</v>
+        <v>142.4403749067821</v>
       </c>
       <c r="E6">
-        <v>-55.75999999999999</v>
+        <v>-54.19999999999999</v>
       </c>
       <c r="F6">
-        <v>6.24</v>
+        <v>7.800000000000001</v>
       </c>
       <c r="G6">
         <v>17</v>
@@ -1779,28 +1779,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M6">
-        <v>0.313872</v>
+        <v>0.39234</v>
       </c>
       <c r="N6">
-        <v>24.96390577777778</v>
+        <v>24.88543777777778</v>
       </c>
       <c r="O6">
-        <v>5.492059271111112</v>
+        <v>5.474796311111112</v>
       </c>
       <c r="P6">
-        <v>19.47184650666667</v>
+        <v>19.41064146666667</v>
       </c>
       <c r="Q6">
-        <v>27.97184650666667</v>
+        <v>27.91064146666667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1061417296890099</v>
+        <v>0.1066415656046191</v>
       </c>
       <c r="T6">
-        <v>0.8780456911365531</v>
+        <v>0.8853189127402076</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>80.53530667844784</v>
+        <v>64.42824534275826</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1032711873243882</v>
+        <v>0.1030769541473268</v>
       </c>
       <c r="C7">
-        <v>151.6403749067821</v>
+        <v>150.5634076897193</v>
       </c>
       <c r="D7">
-        <v>142.4403749067821</v>
+        <v>142.9234076897193</v>
       </c>
       <c r="E7">
-        <v>-54.19999999999999</v>
+        <v>-52.63999999999999</v>
       </c>
       <c r="F7">
-        <v>7.800000000000001</v>
+        <v>9.360000000000001</v>
       </c>
       <c r="G7">
         <v>17</v>
@@ -1861,28 +1861,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M7">
-        <v>0.39234</v>
+        <v>0.4708080000000001</v>
       </c>
       <c r="N7">
-        <v>24.88543777777778</v>
+        <v>24.80696977777778</v>
       </c>
       <c r="O7">
-        <v>5.474796311111112</v>
+        <v>5.457533351111111</v>
       </c>
       <c r="P7">
-        <v>19.41064146666667</v>
+        <v>19.34943642666667</v>
       </c>
       <c r="Q7">
-        <v>27.91064146666667</v>
+        <v>27.84943642666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1066415656046191</v>
+        <v>0.1071520363269434</v>
       </c>
       <c r="T7">
-        <v>0.8853189127402076</v>
+        <v>0.8927468837396842</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>64.42824534275826</v>
+        <v>53.69020445229854</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1030769541473268</v>
+        <v>0.1028827209702655</v>
       </c>
       <c r="C8">
-        <v>150.5634076897193</v>
+        <v>149.4897276667658</v>
       </c>
       <c r="D8">
-        <v>142.9234076897193</v>
+        <v>143.4097276667657</v>
       </c>
       <c r="E8">
-        <v>-52.63999999999999</v>
+        <v>-51.08</v>
       </c>
       <c r="F8">
-        <v>9.359999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G8">
         <v>17</v>
@@ -1943,28 +1943,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M8">
-        <v>0.4708079999999999</v>
+        <v>0.5492759999999999</v>
       </c>
       <c r="N8">
-        <v>24.80696977777778</v>
+        <v>24.72850177777778</v>
       </c>
       <c r="O8">
-        <v>5.457533351111111</v>
+        <v>5.440270391111111</v>
       </c>
       <c r="P8">
-        <v>19.34943642666667</v>
+        <v>19.28823138666667</v>
       </c>
       <c r="Q8">
-        <v>27.84943642666667</v>
+        <v>27.78823138666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1071520363269434</v>
+        <v>0.107673484914264</v>
       </c>
       <c r="T8">
-        <v>0.8927468837396842</v>
+        <v>0.9003345960509777</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>53.69020445229856</v>
+        <v>46.02017524482734</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1028827209702655</v>
+        <v>0.1026884877932042</v>
       </c>
       <c r="C9">
-        <v>149.4897276667657</v>
+        <v>148.4193685081161</v>
       </c>
       <c r="D9">
-        <v>143.4097276667657</v>
+        <v>143.8993685081161</v>
       </c>
       <c r="E9">
-        <v>-51.07999999999999</v>
+        <v>-49.52</v>
       </c>
       <c r="F9">
-        <v>10.92</v>
+        <v>12.48</v>
       </c>
       <c r="G9">
         <v>17</v>
@@ -2025,28 +2025,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M9">
-        <v>0.5492760000000001</v>
+        <v>0.627744</v>
       </c>
       <c r="N9">
-        <v>24.72850177777778</v>
+        <v>24.65003377777778</v>
       </c>
       <c r="O9">
-        <v>5.440270391111111</v>
+        <v>5.423007431111111</v>
       </c>
       <c r="P9">
-        <v>19.28823138666667</v>
+        <v>19.22702634666667</v>
       </c>
       <c r="Q9">
-        <v>27.78823138666667</v>
+        <v>27.72702634666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.107673484914264</v>
+        <v>0.1082062693404393</v>
       </c>
       <c r="T9">
-        <v>0.9003345960509779</v>
+        <v>0.9080872586299081</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>46.02017524482733</v>
+        <v>40.26765333922392</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1026884877932042</v>
+        <v>0.1024942546161428</v>
       </c>
       <c r="C10">
-        <v>148.4193685081161</v>
+        <v>147.3523643453785</v>
       </c>
       <c r="D10">
-        <v>143.8993685081161</v>
+        <v>144.3923643453785</v>
       </c>
       <c r="E10">
-        <v>-49.52</v>
+        <v>-47.95999999999999</v>
       </c>
       <c r="F10">
-        <v>12.48</v>
+        <v>14.04</v>
       </c>
       <c r="G10">
         <v>17</v>
@@ -2107,28 +2107,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M10">
-        <v>0.627744</v>
+        <v>0.706212</v>
       </c>
       <c r="N10">
-        <v>24.65003377777778</v>
+        <v>24.57156577777778</v>
       </c>
       <c r="O10">
-        <v>5.423007431111111</v>
+        <v>5.405744471111111</v>
       </c>
       <c r="P10">
-        <v>19.22702634666667</v>
+        <v>19.16582130666666</v>
       </c>
       <c r="Q10">
-        <v>27.72702634666667</v>
+        <v>27.66582130666666</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1082062693404393</v>
+        <v>0.1087507633144427</v>
       </c>
       <c r="T10">
-        <v>0.9080872586299081</v>
+        <v>0.9160103093973864</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.26765333922392</v>
+        <v>35.79346963486571</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1024942546161428</v>
+        <v>0.1023000214390815</v>
       </c>
       <c r="C11">
-        <v>147.3523643453785</v>
+        <v>146.2887497795051</v>
       </c>
       <c r="D11">
-        <v>144.3923643453785</v>
+        <v>144.888749779505</v>
       </c>
       <c r="E11">
-        <v>-47.95999999999999</v>
+        <v>-46.39999999999999</v>
       </c>
       <c r="F11">
-        <v>14.04</v>
+        <v>15.6</v>
       </c>
       <c r="G11">
         <v>17</v>
@@ -2189,28 +2189,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M11">
-        <v>0.706212</v>
+        <v>0.7846799999999998</v>
       </c>
       <c r="N11">
-        <v>24.57156577777778</v>
+        <v>24.49309777777778</v>
       </c>
       <c r="O11">
-        <v>5.405744471111111</v>
+        <v>5.388481511111111</v>
       </c>
       <c r="P11">
-        <v>19.16582130666666</v>
+        <v>19.10461626666667</v>
       </c>
       <c r="Q11">
-        <v>27.66582130666666</v>
+        <v>27.60461626666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1087507633144427</v>
+        <v>0.109307357154535</v>
       </c>
       <c r="T11">
-        <v>0.9160103093973864</v>
+        <v>0.9241094279596975</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.79346963486571</v>
+        <v>32.21412267137914</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1023000214390815</v>
+        <v>0.1021057882620202</v>
       </c>
       <c r="C12">
-        <v>146.2887497795051</v>
+        <v>145.2285598888877</v>
       </c>
       <c r="D12">
-        <v>144.888749779505</v>
+        <v>145.3885598888877</v>
       </c>
       <c r="E12">
-        <v>-46.39999999999999</v>
+        <v>-44.83999999999999</v>
       </c>
       <c r="F12">
-        <v>15.6</v>
+        <v>17.16</v>
       </c>
       <c r="G12">
         <v>17</v>
@@ -2271,28 +2271,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M12">
-        <v>0.78468</v>
+        <v>0.8631479999999999</v>
       </c>
       <c r="N12">
-        <v>24.49309777777778</v>
+        <v>24.41462977777778</v>
       </c>
       <c r="O12">
-        <v>5.388481511111111</v>
+        <v>5.371218551111111</v>
       </c>
       <c r="P12">
-        <v>19.10461626666667</v>
+        <v>19.04341122666667</v>
       </c>
       <c r="Q12">
-        <v>27.60461626666667</v>
+        <v>27.54341122666667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.109307357154535</v>
+        <v>0.109876458721371</v>
       </c>
       <c r="T12">
-        <v>0.9241094279596975</v>
+        <v>0.9323905491863304</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.21412267137913</v>
+        <v>29.28556606489013</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1021057882620202</v>
+        <v>0.1019115550849589</v>
       </c>
       <c r="C13">
-        <v>145.2285598888877</v>
+        <v>144.1718302376212</v>
       </c>
       <c r="D13">
-        <v>145.3885598888877</v>
+        <v>145.8918302376212</v>
       </c>
       <c r="E13">
-        <v>-44.83999999999999</v>
+        <v>-43.27999999999999</v>
       </c>
       <c r="F13">
-        <v>17.16</v>
+        <v>18.72</v>
       </c>
       <c r="G13">
         <v>17</v>
@@ -2353,28 +2353,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M13">
-        <v>0.8631479999999999</v>
+        <v>0.9416159999999999</v>
       </c>
       <c r="N13">
-        <v>24.41462977777778</v>
+        <v>24.33616177777778</v>
       </c>
       <c r="O13">
-        <v>5.371218551111111</v>
+        <v>5.353955591111111</v>
       </c>
       <c r="P13">
-        <v>19.04341122666667</v>
+        <v>18.98220618666667</v>
       </c>
       <c r="Q13">
-        <v>27.54341122666667</v>
+        <v>27.48220618666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.109876458721371</v>
+        <v>0.110458494414726</v>
       </c>
       <c r="T13">
-        <v>0.9323905491863304</v>
+        <v>0.9408598777135683</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.28556606489013</v>
+        <v>26.84510222614928</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1019115550849589</v>
+        <v>0.1017173219078975</v>
       </c>
       <c r="C14">
-        <v>144.1718302376212</v>
+        <v>143.1185968839393</v>
       </c>
       <c r="D14">
-        <v>145.8918302376212</v>
+        <v>146.3985968839393</v>
       </c>
       <c r="E14">
-        <v>-43.27999999999999</v>
+        <v>-41.71999999999999</v>
       </c>
       <c r="F14">
-        <v>18.72</v>
+        <v>20.28</v>
       </c>
       <c r="G14">
         <v>17</v>
@@ -2435,28 +2435,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M14">
-        <v>0.9416159999999999</v>
+        <v>1.020084</v>
       </c>
       <c r="N14">
-        <v>24.33616177777778</v>
+        <v>24.25769377777778</v>
       </c>
       <c r="O14">
-        <v>5.353955591111111</v>
+        <v>5.336692631111111</v>
       </c>
       <c r="P14">
-        <v>18.98220618666667</v>
+        <v>18.92100114666667</v>
       </c>
       <c r="Q14">
-        <v>27.48220618666667</v>
+        <v>27.42100114666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.110458494414726</v>
+        <v>0.1110539102389627</v>
       </c>
       <c r="T14">
-        <v>0.9408598777135683</v>
+        <v>0.9495239034483289</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.84510222614928</v>
+        <v>24.78009436259933</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1017173219078975</v>
+        <v>0.1015230887308362</v>
       </c>
       <c r="C15">
-        <v>143.1185968839393</v>
+        <v>142.0688963888256</v>
       </c>
       <c r="D15">
-        <v>146.3985968839393</v>
+        <v>146.9088963888256</v>
       </c>
       <c r="E15">
-        <v>-41.71999999999999</v>
+        <v>-40.15999999999999</v>
       </c>
       <c r="F15">
-        <v>20.28</v>
+        <v>21.84</v>
       </c>
       <c r="G15">
         <v>17</v>
@@ -2517,28 +2517,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M15">
-        <v>1.020084</v>
+        <v>1.098552</v>
       </c>
       <c r="N15">
-        <v>24.25769377777778</v>
+        <v>24.17922577777778</v>
       </c>
       <c r="O15">
-        <v>5.336692631111111</v>
+        <v>5.319429671111111</v>
       </c>
       <c r="P15">
-        <v>18.92100114666667</v>
+        <v>18.85979610666666</v>
       </c>
       <c r="Q15">
-        <v>27.42100114666667</v>
+        <v>27.35979610666666</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1110539102389627</v>
+        <v>0.1116631729428328</v>
       </c>
       <c r="T15">
-        <v>0.9495239034483289</v>
+        <v>0.9583894181536655</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.78009436259933</v>
+        <v>23.01008762241366</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1015230887308362</v>
+        <v>0.1013288555537749</v>
       </c>
       <c r="C16">
-        <v>142.0688963888256</v>
+        <v>141.0227658248082</v>
       </c>
       <c r="D16">
-        <v>146.9088963888256</v>
+        <v>147.4227658248082</v>
       </c>
       <c r="E16">
-        <v>-40.15999999999999</v>
+        <v>-38.59999999999999</v>
       </c>
       <c r="F16">
-        <v>21.84</v>
+        <v>23.4</v>
       </c>
       <c r="G16">
         <v>17</v>
@@ -2599,28 +2599,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M16">
-        <v>1.098552</v>
+        <v>1.17702</v>
       </c>
       <c r="N16">
-        <v>24.17922577777778</v>
+        <v>24.10075777777778</v>
       </c>
       <c r="O16">
-        <v>5.319429671111111</v>
+        <v>5.302166711111112</v>
       </c>
       <c r="P16">
-        <v>18.85979610666666</v>
+        <v>18.79859106666667</v>
       </c>
       <c r="Q16">
-        <v>27.35979610666666</v>
+        <v>27.29859106666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1116631729428328</v>
+        <v>0.1122867712397351</v>
       </c>
       <c r="T16">
-        <v>0.9583894181536655</v>
+        <v>0.9674635332050099</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.01008762241366</v>
+        <v>21.47608178091943</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1013288555537749</v>
+        <v>0.1011346223767135</v>
       </c>
       <c r="C17">
-        <v>141.0227658248082</v>
+        <v>139.980242784936</v>
       </c>
       <c r="D17">
-        <v>147.4227658248082</v>
+        <v>147.940242784936</v>
       </c>
       <c r="E17">
-        <v>-38.59999999999999</v>
+        <v>-37.03999999999999</v>
       </c>
       <c r="F17">
-        <v>23.4</v>
+        <v>24.96</v>
       </c>
       <c r="G17">
         <v>17</v>
@@ -2681,28 +2681,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M17">
-        <v>1.17702</v>
+        <v>1.255488</v>
       </c>
       <c r="N17">
-        <v>24.10075777777778</v>
+        <v>24.02228977777778</v>
       </c>
       <c r="O17">
-        <v>5.302166711111112</v>
+        <v>5.284903751111111</v>
       </c>
       <c r="P17">
-        <v>18.79859106666667</v>
+        <v>18.73738602666667</v>
       </c>
       <c r="Q17">
-        <v>27.29859106666667</v>
+        <v>27.23738602666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1122867712397351</v>
+        <v>0.1129252171151352</v>
       </c>
       <c r="T17">
-        <v>0.9674635332050099</v>
+        <v>0.9767536986147197</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.47608178091943</v>
+        <v>20.13382666961196</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1011346223767135</v>
+        <v>0.1009403891996522</v>
       </c>
       <c r="C18">
-        <v>139.980242784936</v>
+        <v>138.9413653919473</v>
       </c>
       <c r="D18">
-        <v>147.940242784936</v>
+        <v>148.4613653919473</v>
       </c>
       <c r="E18">
-        <v>-37.03999999999999</v>
+        <v>-35.47999999999999</v>
       </c>
       <c r="F18">
-        <v>24.96</v>
+        <v>26.52</v>
       </c>
       <c r="G18">
         <v>17</v>
@@ -2763,28 +2763,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M18">
-        <v>1.255488</v>
+        <v>1.333956</v>
       </c>
       <c r="N18">
-        <v>24.02228977777778</v>
+        <v>23.94382177777778</v>
       </c>
       <c r="O18">
-        <v>5.284903751111111</v>
+        <v>5.267640791111111</v>
       </c>
       <c r="P18">
-        <v>18.73738602666667</v>
+        <v>18.67618098666667</v>
       </c>
       <c r="Q18">
-        <v>27.23738602666667</v>
+        <v>27.17618098666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1129252171151352</v>
+        <v>0.1135790472284967</v>
       </c>
       <c r="T18">
-        <v>0.9767536986147197</v>
+        <v>0.9862677234318925</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.13382666961196</v>
+        <v>18.94948392434067</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1009403891996522</v>
+        <v>0.1007461560225909</v>
       </c>
       <c r="C19">
-        <v>138.9413653919473</v>
+        <v>137.9061723076319</v>
       </c>
       <c r="D19">
-        <v>148.4613653919473</v>
+        <v>148.9861723076319</v>
       </c>
       <c r="E19">
-        <v>-35.47999999999999</v>
+        <v>-33.91999999999999</v>
       </c>
       <c r="F19">
-        <v>26.52</v>
+        <v>28.08</v>
       </c>
       <c r="G19">
         <v>17</v>
@@ -2845,28 +2845,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M19">
-        <v>1.333956</v>
+        <v>1.412424</v>
       </c>
       <c r="N19">
-        <v>23.94382177777778</v>
+        <v>23.86535377777778</v>
       </c>
       <c r="O19">
-        <v>5.267640791111111</v>
+        <v>5.250377831111111</v>
       </c>
       <c r="P19">
-        <v>18.67618098666667</v>
+        <v>18.61497594666667</v>
       </c>
       <c r="Q19">
-        <v>27.17618098666667</v>
+        <v>27.11497594666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1135790472284967</v>
+        <v>0.1142488244177938</v>
       </c>
       <c r="T19">
-        <v>0.9862677234318925</v>
+        <v>0.9960137976348499</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.94948392434067</v>
+        <v>17.89673481743285</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1007461560225909</v>
+        <v>0.1005519228455296</v>
       </c>
       <c r="C20">
-        <v>137.9061723076319</v>
+        <v>136.8747027423923</v>
       </c>
       <c r="D20">
-        <v>148.9861723076319</v>
+        <v>149.5147027423923</v>
       </c>
       <c r="E20">
-        <v>-33.91999999999999</v>
+        <v>-32.35999999999999</v>
       </c>
       <c r="F20">
-        <v>28.08</v>
+        <v>29.64</v>
       </c>
       <c r="G20">
         <v>17</v>
@@ -2927,28 +2927,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M20">
-        <v>1.412424</v>
+        <v>1.490892</v>
       </c>
       <c r="N20">
-        <v>23.86535377777778</v>
+        <v>23.78688577777778</v>
       </c>
       <c r="O20">
-        <v>5.250377831111111</v>
+        <v>5.233114871111112</v>
       </c>
       <c r="P20">
-        <v>18.61497594666667</v>
+        <v>18.55377090666667</v>
       </c>
       <c r="Q20">
-        <v>27.11497594666667</v>
+        <v>27.05377090666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1142488244177937</v>
+        <v>0.1149351393154686</v>
       </c>
       <c r="T20">
-        <v>0.9960137976348498</v>
+        <v>1.006000515645288</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.89673481743285</v>
+        <v>16.95480140598902</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1005519228455296</v>
+        <v>0.1003576896684682</v>
       </c>
       <c r="C21">
-        <v>136.8747027423923</v>
+        <v>135.8469964650097</v>
       </c>
       <c r="D21">
-        <v>149.5147027423923</v>
+        <v>150.0469964650097</v>
       </c>
       <c r="E21">
-        <v>-32.35999999999999</v>
+        <v>-30.79999999999999</v>
       </c>
       <c r="F21">
-        <v>29.64</v>
+        <v>31.2</v>
       </c>
       <c r="G21">
         <v>17</v>
@@ -3009,28 +3009,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M21">
-        <v>1.490892</v>
+        <v>1.56936</v>
       </c>
       <c r="N21">
-        <v>23.78688577777778</v>
+        <v>23.70841777777778</v>
       </c>
       <c r="O21">
-        <v>5.233114871111112</v>
+        <v>5.215851911111112</v>
       </c>
       <c r="P21">
-        <v>18.55377090666667</v>
+        <v>18.49256586666667</v>
       </c>
       <c r="Q21">
-        <v>27.05377090666667</v>
+        <v>26.99256586666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1149351393154686</v>
+        <v>0.1156386120855853</v>
       </c>
       <c r="T21">
-        <v>1.006000515645288</v>
+        <v>1.016236901605986</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.95480140598902</v>
+        <v>16.10706133568956</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1003576896684682</v>
+        <v>0.1001634564914069</v>
       </c>
       <c r="C22">
-        <v>135.8469964650097</v>
+        <v>134.8230938126189</v>
       </c>
       <c r="D22">
-        <v>150.0469964650097</v>
+        <v>150.5830938126189</v>
       </c>
       <c r="E22">
-        <v>-30.79999999999999</v>
+        <v>-29.23999999999999</v>
       </c>
       <c r="F22">
-        <v>31.2</v>
+        <v>32.76000000000001</v>
       </c>
       <c r="G22">
         <v>17</v>
@@ -3091,28 +3091,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M22">
-        <v>1.56936</v>
+        <v>1.647828</v>
       </c>
       <c r="N22">
-        <v>23.70841777777778</v>
+        <v>23.62994977777778</v>
       </c>
       <c r="O22">
-        <v>5.215851911111112</v>
+        <v>5.198588951111112</v>
       </c>
       <c r="P22">
-        <v>18.49256586666667</v>
+        <v>18.43136082666667</v>
       </c>
       <c r="Q22">
-        <v>26.99256586666667</v>
+        <v>26.93136082666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1156386120855853</v>
+        <v>0.1163598942929201</v>
       </c>
       <c r="T22">
-        <v>1.016236901605986</v>
+        <v>1.026732436578349</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.10706133568956</v>
+        <v>15.34005841494244</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1001634564914069</v>
+        <v>0.09996922331434557</v>
       </c>
       <c r="C23">
-        <v>134.8230938126189</v>
+        <v>133.8030357008978</v>
       </c>
       <c r="D23">
-        <v>150.5830938126189</v>
+        <v>151.1230357008978</v>
       </c>
       <c r="E23">
-        <v>-29.23999999999999</v>
+        <v>-27.67999999999999</v>
       </c>
       <c r="F23">
-        <v>32.76</v>
+        <v>34.32</v>
       </c>
       <c r="G23">
         <v>17</v>
@@ -3173,28 +3173,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M23">
-        <v>1.647828</v>
+        <v>1.726296</v>
       </c>
       <c r="N23">
-        <v>23.62994977777778</v>
+        <v>23.55148177777778</v>
       </c>
       <c r="O23">
-        <v>5.198588951111112</v>
+        <v>5.181325991111111</v>
       </c>
       <c r="P23">
-        <v>18.43136082666667</v>
+        <v>18.37015578666666</v>
       </c>
       <c r="Q23">
-        <v>26.93136082666667</v>
+        <v>26.87015578666666</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1163598942929201</v>
+        <v>0.1170996709158277</v>
       </c>
       <c r="T23">
-        <v>1.026732436578348</v>
+        <v>1.037497087832053</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.34005841494245</v>
+        <v>14.64278303244506</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09996922331434557</v>
+        <v>0.09977499013728425</v>
       </c>
       <c r="C24">
-        <v>133.8030357008978</v>
+        <v>132.7868636344774</v>
       </c>
       <c r="D24">
-        <v>151.1230357008978</v>
+        <v>151.6668636344774</v>
       </c>
       <c r="E24">
-        <v>-27.67999999999999</v>
+        <v>-26.11999999999999</v>
       </c>
       <c r="F24">
-        <v>34.32</v>
+        <v>35.88</v>
       </c>
       <c r="G24">
         <v>17</v>
@@ -3255,28 +3255,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M24">
-        <v>1.726296</v>
+        <v>1.804764</v>
       </c>
       <c r="N24">
-        <v>23.55148177777778</v>
+        <v>23.47301377777778</v>
       </c>
       <c r="O24">
-        <v>5.181325991111111</v>
+        <v>5.164063031111112</v>
       </c>
       <c r="P24">
-        <v>18.37015578666666</v>
+        <v>18.30895074666667</v>
       </c>
       <c r="Q24">
-        <v>26.87015578666666</v>
+        <v>26.80895074666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1170996709158277</v>
+        <v>0.1178586625159536</v>
       </c>
       <c r="T24">
-        <v>1.037497087832053</v>
+        <v>1.048541340417023</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.64278303244506</v>
+        <v>14.00614029190397</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09977499013728425</v>
+        <v>0.09958075696022292</v>
       </c>
       <c r="C25">
-        <v>132.7868636344774</v>
+        <v>131.7746197175768</v>
       </c>
       <c r="D25">
-        <v>151.6668636344774</v>
+        <v>152.2146197175768</v>
       </c>
       <c r="E25">
-        <v>-26.11999999999999</v>
+        <v>-24.55999999999999</v>
       </c>
       <c r="F25">
-        <v>35.88</v>
+        <v>37.44</v>
       </c>
       <c r="G25">
         <v>17</v>
@@ -3337,28 +3337,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M25">
-        <v>1.804764</v>
+        <v>1.883232</v>
       </c>
       <c r="N25">
-        <v>23.47301377777778</v>
+        <v>23.39454577777778</v>
       </c>
       <c r="O25">
-        <v>5.164063031111112</v>
+        <v>5.146800071111111</v>
       </c>
       <c r="P25">
-        <v>18.30895074666667</v>
+        <v>18.24774570666667</v>
       </c>
       <c r="Q25">
-        <v>26.80895074666667</v>
+        <v>26.74774570666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1178586625159536</v>
+        <v>0.1186376275792407</v>
       </c>
       <c r="T25">
-        <v>1.048541340417023</v>
+        <v>1.059876231227913</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.00614029190397</v>
+        <v>13.42255111307464</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09958075696022292</v>
+        <v>0.0993865237831616</v>
       </c>
       <c r="C26">
-        <v>131.7746197175768</v>
+        <v>130.7663466648698</v>
       </c>
       <c r="D26">
-        <v>152.2146197175768</v>
+        <v>152.7663466648698</v>
       </c>
       <c r="E26">
-        <v>-24.56</v>
+        <v>-22.99999999999999</v>
       </c>
       <c r="F26">
-        <v>37.44</v>
+        <v>39</v>
       </c>
       <c r="G26">
         <v>17</v>
@@ -3419,28 +3419,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M26">
-        <v>1.883232</v>
+        <v>1.9617</v>
       </c>
       <c r="N26">
-        <v>23.39454577777778</v>
+        <v>23.31607777777778</v>
       </c>
       <c r="O26">
-        <v>5.146800071111111</v>
+        <v>5.129537111111111</v>
       </c>
       <c r="P26">
-        <v>18.24774570666667</v>
+        <v>18.18654066666667</v>
       </c>
       <c r="Q26">
-        <v>26.74774570666667</v>
+        <v>26.68654066666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1186376275792407</v>
+        <v>0.1194373650442155</v>
       </c>
       <c r="T26">
-        <v>1.059876231227913</v>
+        <v>1.07151338579376</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.42255111307464</v>
+        <v>12.88564906855165</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0993865237831616</v>
+        <v>0.09949649060610025</v>
       </c>
       <c r="C27">
-        <v>130.7663466648698</v>
+        <v>128.8934913999342</v>
       </c>
       <c r="D27">
-        <v>152.7663466648698</v>
+        <v>152.4534913999342</v>
       </c>
       <c r="E27">
-        <v>-22.99999999999999</v>
+        <v>-21.43999999999999</v>
       </c>
       <c r="F27">
-        <v>39</v>
+        <v>40.56</v>
       </c>
       <c r="G27">
         <v>17</v>
@@ -3501,45 +3501,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M27">
-        <v>1.9617</v>
+        <v>2.101008</v>
       </c>
       <c r="N27">
-        <v>23.31607777777778</v>
+        <v>23.17676977777778</v>
       </c>
       <c r="O27">
-        <v>5.129537111111111</v>
+        <v>5.098889351111112</v>
       </c>
       <c r="P27">
-        <v>18.18654066666667</v>
+        <v>18.07788042666667</v>
       </c>
       <c r="Q27">
-        <v>26.68654066666667</v>
+        <v>26.57788042666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1194373650442155</v>
+        <v>0.1202587170352706</v>
       </c>
       <c r="T27">
-        <v>1.07151338579376</v>
+        <v>1.083465058050576</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>12.88564906855165</v>
+        <v>12.03126203126203</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09949649060610025</v>
+        <v>0.09931395742903892</v>
       </c>
       <c r="C28">
-        <v>128.8934913999342</v>
+        <v>127.853501907029</v>
       </c>
       <c r="D28">
-        <v>152.4534913999342</v>
+        <v>152.973501907029</v>
       </c>
       <c r="E28">
-        <v>-21.43999999999999</v>
+        <v>-19.87999999999999</v>
       </c>
       <c r="F28">
-        <v>40.56</v>
+        <v>42.12</v>
       </c>
       <c r="G28">
         <v>17</v>
@@ -3583,28 +3583,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M28">
-        <v>2.101008</v>
+        <v>2.181816</v>
       </c>
       <c r="N28">
-        <v>23.17676977777778</v>
+        <v>23.09596177777778</v>
       </c>
       <c r="O28">
-        <v>5.098889351111112</v>
+        <v>5.081111591111111</v>
       </c>
       <c r="P28">
-        <v>18.07788042666667</v>
+        <v>18.01485018666667</v>
       </c>
       <c r="Q28">
-        <v>26.57788042666667</v>
+        <v>26.51485018666667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1202587170352706</v>
+        <v>0.1211025718206013</v>
       </c>
       <c r="T28">
-        <v>1.083465058050576</v>
+        <v>1.095744173382921</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.03126203126203</v>
+        <v>11.58565973380788</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09931395742903892</v>
+        <v>0.0991314242519776</v>
       </c>
       <c r="C29">
-        <v>127.853501907029</v>
+        <v>126.8170720104141</v>
       </c>
       <c r="D29">
-        <v>152.973501907029</v>
+        <v>153.4970720104141</v>
       </c>
       <c r="E29">
-        <v>-19.87999999999999</v>
+        <v>-18.31999999999999</v>
       </c>
       <c r="F29">
-        <v>42.12</v>
+        <v>43.68000000000001</v>
       </c>
       <c r="G29">
         <v>17</v>
@@ -3665,28 +3665,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M29">
-        <v>2.181816</v>
+        <v>2.262624</v>
       </c>
       <c r="N29">
-        <v>23.09596177777778</v>
+        <v>23.01515377777778</v>
       </c>
       <c r="O29">
-        <v>5.081111591111111</v>
+        <v>5.063333831111112</v>
       </c>
       <c r="P29">
-        <v>18.01485018666667</v>
+        <v>17.95181994666667</v>
       </c>
       <c r="Q29">
-        <v>26.51485018666667</v>
+        <v>26.45181994666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1211025718206013</v>
+        <v>0.1219698670166356</v>
       </c>
       <c r="T29">
-        <v>1.095744173382921</v>
+        <v>1.108364375252275</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.58565973380788</v>
+        <v>11.17188617188617</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0991314242519776</v>
+        <v>0.09894889107491628</v>
       </c>
       <c r="C30">
-        <v>126.8170720104141</v>
+        <v>125.7842383850461</v>
       </c>
       <c r="D30">
-        <v>153.4970720104141</v>
+        <v>154.0242383850461</v>
       </c>
       <c r="E30">
-        <v>-18.31999999999999</v>
+        <v>-16.75999999999998</v>
       </c>
       <c r="F30">
-        <v>43.68000000000001</v>
+        <v>45.24000000000001</v>
       </c>
       <c r="G30">
         <v>17</v>
@@ -3747,28 +3747,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M30">
-        <v>2.262624</v>
+        <v>2.343432</v>
       </c>
       <c r="N30">
-        <v>23.01515377777778</v>
+        <v>22.93434577777778</v>
       </c>
       <c r="O30">
-        <v>5.063333831111112</v>
+        <v>5.045556071111111</v>
       </c>
       <c r="P30">
-        <v>17.95181994666667</v>
+        <v>17.88878970666667</v>
       </c>
       <c r="Q30">
-        <v>26.45181994666667</v>
+        <v>26.38878970666667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1219698670166356</v>
+        <v>0.1228615930632624</v>
       </c>
       <c r="T30">
-        <v>1.108364375252275</v>
+        <v>1.121340075765837</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.17188617188617</v>
+        <v>10.7866487176832</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09894889107491628</v>
+        <v>0.09876635789785493</v>
       </c>
       <c r="C31">
-        <v>125.7842383850461</v>
+        <v>124.7550382114396</v>
       </c>
       <c r="D31">
-        <v>154.0242383850461</v>
+        <v>154.5550382114396</v>
       </c>
       <c r="E31">
-        <v>-16.76</v>
+        <v>-15.2</v>
       </c>
       <c r="F31">
-        <v>45.23999999999999</v>
+        <v>46.8</v>
       </c>
       <c r="G31">
         <v>17</v>
@@ -3829,28 +3829,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M31">
-        <v>2.343432</v>
+        <v>2.42424</v>
       </c>
       <c r="N31">
-        <v>22.93434577777778</v>
+        <v>22.85353777777778</v>
       </c>
       <c r="O31">
-        <v>5.045556071111111</v>
+        <v>5.027778311111111</v>
       </c>
       <c r="P31">
-        <v>17.88878970666667</v>
+        <v>17.82575946666667</v>
       </c>
       <c r="Q31">
-        <v>26.38878970666667</v>
+        <v>26.32575946666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1228615930632624</v>
+        <v>0.1237787969969356</v>
       </c>
       <c r="T31">
-        <v>1.121340075765837</v>
+        <v>1.134686510579786</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.7866487176832</v>
+        <v>10.42709376042709</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09876635789785493</v>
+        <v>0.09858382472079361</v>
       </c>
       <c r="C32">
-        <v>124.7550382114396</v>
+        <v>123.7295091844089</v>
       </c>
       <c r="D32">
-        <v>154.5550382114396</v>
+        <v>155.0895091844089</v>
       </c>
       <c r="E32">
-        <v>-15.2</v>
+        <v>-13.63999999999999</v>
       </c>
       <c r="F32">
-        <v>46.8</v>
+        <v>48.36</v>
       </c>
       <c r="G32">
         <v>17</v>
@@ -3911,28 +3911,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M32">
-        <v>2.42424</v>
+        <v>2.505048</v>
       </c>
       <c r="N32">
-        <v>22.85353777777778</v>
+        <v>22.77272977777778</v>
       </c>
       <c r="O32">
-        <v>5.027778311111111</v>
+        <v>5.010000551111111</v>
       </c>
       <c r="P32">
-        <v>17.82575946666667</v>
+        <v>17.76272922666667</v>
       </c>
       <c r="Q32">
-        <v>26.32575946666667</v>
+        <v>26.26272922666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1237787969969356</v>
+        <v>0.1247225865518748</v>
       </c>
       <c r="T32">
-        <v>1.134686510579786</v>
+        <v>1.148419798576749</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.42709376042709</v>
+        <v>10.09073589718751</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09858382472079361</v>
+        <v>0.09882561154373228</v>
       </c>
       <c r="C33">
-        <v>123.7295091844089</v>
+        <v>121.4623301702473</v>
       </c>
       <c r="D33">
-        <v>155.0895091844089</v>
+        <v>154.3823301702473</v>
       </c>
       <c r="E33">
-        <v>-13.63999999999999</v>
+        <v>-12.07999999999999</v>
       </c>
       <c r="F33">
-        <v>48.36</v>
+        <v>49.92</v>
       </c>
       <c r="G33">
         <v>17</v>
@@ -3993,45 +3993,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M33">
-        <v>2.505048</v>
+        <v>2.67072</v>
       </c>
       <c r="N33">
-        <v>22.77272977777778</v>
+        <v>22.60705777777778</v>
       </c>
       <c r="O33">
-        <v>5.010000551111111</v>
+        <v>4.973552711111111</v>
       </c>
       <c r="P33">
-        <v>17.76272922666667</v>
+        <v>17.63350506666667</v>
       </c>
       <c r="Q33">
-        <v>26.26272922666667</v>
+        <v>26.13350506666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1247225865518748</v>
+        <v>0.1256941346231357</v>
       </c>
       <c r="T33">
-        <v>1.148419798576749</v>
+        <v>1.162557006808916</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>10.09073589718751</v>
+        <v>9.46478020076151</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09882561154373228</v>
+        <v>0.09865633836667095</v>
       </c>
       <c r="C34">
-        <v>121.4623301702473</v>
+        <v>120.3967417832645</v>
       </c>
       <c r="D34">
-        <v>154.3823301702473</v>
+        <v>154.8767417832645</v>
       </c>
       <c r="E34">
-        <v>-12.07999999999999</v>
+        <v>-10.51999999999999</v>
       </c>
       <c r="F34">
-        <v>49.92</v>
+        <v>51.48</v>
       </c>
       <c r="G34">
         <v>17</v>
@@ -4075,28 +4075,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M34">
-        <v>2.67072</v>
+        <v>2.75418</v>
       </c>
       <c r="N34">
-        <v>22.60705777777778</v>
+        <v>22.52359777777778</v>
       </c>
       <c r="O34">
-        <v>4.973552711111111</v>
+        <v>4.955191511111111</v>
       </c>
       <c r="P34">
-        <v>17.63350506666667</v>
+        <v>17.56840626666667</v>
       </c>
       <c r="Q34">
-        <v>26.13350506666667</v>
+        <v>26.06840626666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1256941346231357</v>
+        <v>0.1266946841293596</v>
       </c>
       <c r="T34">
-        <v>1.162557006808916</v>
+        <v>1.177116221256968</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.46478020076151</v>
+        <v>9.177968679526311</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09865633836667095</v>
+        <v>0.0984870651896096</v>
       </c>
       <c r="C35">
-        <v>120.3967417832645</v>
+        <v>119.3343302908083</v>
       </c>
       <c r="D35">
-        <v>154.8767417832645</v>
+        <v>155.3743302908083</v>
       </c>
       <c r="E35">
-        <v>-10.51999999999999</v>
+        <v>-8.959999999999987</v>
       </c>
       <c r="F35">
-        <v>51.48</v>
+        <v>53.04000000000001</v>
       </c>
       <c r="G35">
         <v>17</v>
@@ -4157,28 +4157,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M35">
-        <v>2.75418</v>
+        <v>2.83764</v>
       </c>
       <c r="N35">
-        <v>22.52359777777778</v>
+        <v>22.44013777777778</v>
       </c>
       <c r="O35">
-        <v>4.955191511111111</v>
+        <v>4.936830311111112</v>
       </c>
       <c r="P35">
-        <v>17.56840626666667</v>
+        <v>17.50330746666667</v>
       </c>
       <c r="Q35">
-        <v>26.06840626666667</v>
+        <v>26.00330746666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1266946841293596</v>
+        <v>0.1277255533175903</v>
       </c>
       <c r="T35">
-        <v>1.177116221256968</v>
+        <v>1.192116624021629</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.177968679526311</v>
+        <v>8.908028424246126</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0984870651896096</v>
+        <v>0.09831779201254831</v>
       </c>
       <c r="C36">
-        <v>119.3343302908083</v>
+        <v>118.2751264117841</v>
       </c>
       <c r="D36">
-        <v>155.3743302908083</v>
+        <v>155.8751264117841</v>
       </c>
       <c r="E36">
-        <v>-8.959999999999987</v>
+        <v>-7.399999999999984</v>
       </c>
       <c r="F36">
-        <v>53.04000000000001</v>
+        <v>54.60000000000001</v>
       </c>
       <c r="G36">
         <v>17</v>
@@ -4239,28 +4239,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M36">
-        <v>2.83764</v>
+        <v>2.9211</v>
       </c>
       <c r="N36">
-        <v>22.44013777777778</v>
+        <v>22.35667777777778</v>
       </c>
       <c r="O36">
-        <v>4.936830311111112</v>
+        <v>4.918469111111111</v>
       </c>
       <c r="P36">
-        <v>17.50330746666667</v>
+        <v>17.43820866666667</v>
       </c>
       <c r="Q36">
-        <v>26.00330746666667</v>
+        <v>25.93820866666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1277255533175903</v>
+        <v>0.1287881415577666</v>
       </c>
       <c r="T36">
-        <v>1.192116624021629</v>
+        <v>1.207578577640587</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.908028424246126</v>
+        <v>8.653513326410522</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09831779201254831</v>
+        <v>0.09814851883548696</v>
       </c>
       <c r="C37">
-        <v>118.2751264117841</v>
+        <v>117.2191612624258</v>
       </c>
       <c r="D37">
-        <v>155.8751264117841</v>
+        <v>156.3791612624258</v>
       </c>
       <c r="E37">
-        <v>-7.399999999999984</v>
+        <v>-5.839999999999989</v>
       </c>
       <c r="F37">
-        <v>54.60000000000001</v>
+        <v>56.16</v>
       </c>
       <c r="G37">
         <v>17</v>
@@ -4321,28 +4321,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M37">
-        <v>2.9211</v>
+        <v>3.00456</v>
       </c>
       <c r="N37">
-        <v>22.35667777777778</v>
+        <v>22.27321777777778</v>
       </c>
       <c r="O37">
-        <v>4.918469111111111</v>
+        <v>4.900107911111111</v>
       </c>
       <c r="P37">
-        <v>17.43820866666667</v>
+        <v>17.37310986666667</v>
       </c>
       <c r="Q37">
-        <v>25.93820866666667</v>
+        <v>25.87310986666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1287881415577666</v>
+        <v>0.1298839356804484</v>
       </c>
       <c r="T37">
-        <v>1.207578577640587</v>
+        <v>1.223523717310137</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.653513326410522</v>
+        <v>8.413137956232452</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09814851883548698</v>
+        <v>0.09797924565842563</v>
       </c>
       <c r="C38">
-        <v>117.2191612624258</v>
+        <v>116.1664663627402</v>
       </c>
       <c r="D38">
-        <v>156.3791612624258</v>
+        <v>156.8864663627402</v>
       </c>
       <c r="E38">
-        <v>-5.839999999999996</v>
+        <v>-4.279999999999994</v>
       </c>
       <c r="F38">
-        <v>56.16</v>
+        <v>57.72</v>
       </c>
       <c r="G38">
         <v>17</v>
@@ -4403,28 +4403,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M38">
-        <v>3.00456</v>
+        <v>3.08802</v>
       </c>
       <c r="N38">
-        <v>22.27321777777778</v>
+        <v>22.18975777777778</v>
       </c>
       <c r="O38">
-        <v>4.900107911111112</v>
+        <v>4.881746711111111</v>
       </c>
       <c r="P38">
-        <v>17.37310986666667</v>
+        <v>17.30801106666667</v>
       </c>
       <c r="Q38">
-        <v>25.87310986666667</v>
+        <v>25.80801106666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1298839356804484</v>
+        <v>0.1310145169181359</v>
       </c>
       <c r="T38">
-        <v>1.223523717310136</v>
+        <v>1.239975051889831</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.413137956232454</v>
+        <v>8.185755849307252</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09797924565842563</v>
+        <v>0.0978099724813643</v>
       </c>
       <c r="C39">
-        <v>116.1664663627402</v>
+        <v>115.1170736430779</v>
       </c>
       <c r="D39">
-        <v>156.8864663627402</v>
+        <v>157.3970736430779</v>
       </c>
       <c r="E39">
-        <v>-4.279999999999994</v>
+        <v>-2.719999999999992</v>
       </c>
       <c r="F39">
-        <v>57.72</v>
+        <v>59.28</v>
       </c>
       <c r="G39">
         <v>17</v>
@@ -4485,28 +4485,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M39">
-        <v>3.08802</v>
+        <v>3.17148</v>
       </c>
       <c r="N39">
-        <v>22.18975777777778</v>
+        <v>22.10629777777778</v>
       </c>
       <c r="O39">
-        <v>4.881746711111111</v>
+        <v>4.863385511111112</v>
       </c>
       <c r="P39">
-        <v>17.30801106666667</v>
+        <v>17.24291226666667</v>
       </c>
       <c r="Q39">
-        <v>25.80801106666667</v>
+        <v>25.74291226666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1310145169181359</v>
+        <v>0.1321815685183295</v>
       </c>
       <c r="T39">
-        <v>1.239975051889831</v>
+        <v>1.256957074681773</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.185755849307252</v>
+        <v>7.970341221693904</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0978099724813643</v>
+        <v>0.09764069930430298</v>
       </c>
       <c r="C40">
-        <v>115.1170736430779</v>
+        <v>114.0710154508325</v>
       </c>
       <c r="D40">
-        <v>157.3970736430779</v>
+        <v>157.9110154508325</v>
       </c>
       <c r="E40">
-        <v>-2.719999999999992</v>
+        <v>-1.159999999999989</v>
       </c>
       <c r="F40">
-        <v>59.28</v>
+        <v>60.84</v>
       </c>
       <c r="G40">
         <v>17</v>
@@ -4567,28 +4567,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M40">
-        <v>3.17148</v>
+        <v>3.25494</v>
       </c>
       <c r="N40">
-        <v>22.10629777777778</v>
+        <v>22.02283777777778</v>
       </c>
       <c r="O40">
-        <v>4.863385511111112</v>
+        <v>4.845024311111111</v>
       </c>
       <c r="P40">
-        <v>17.24291226666667</v>
+        <v>17.17781346666667</v>
       </c>
       <c r="Q40">
-        <v>25.74291226666667</v>
+        <v>25.67781346666667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1321815685183295</v>
+        <v>0.1333868841054147</v>
       </c>
       <c r="T40">
-        <v>1.256957074681773</v>
+        <v>1.274495885106239</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.970341221693904</v>
+        <v>7.765973498060726</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09764069930430298</v>
+        <v>0.09772102612724165</v>
       </c>
       <c r="C41">
-        <v>114.0710154508325</v>
+        <v>112.2667119167094</v>
       </c>
       <c r="D41">
-        <v>157.9110154508325</v>
+        <v>157.6667119167094</v>
       </c>
       <c r="E41">
-        <v>-1.159999999999989</v>
+        <v>0.4000000000000128</v>
       </c>
       <c r="F41">
-        <v>60.84</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="G41">
         <v>17</v>
@@ -4649,45 +4649,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M41">
-        <v>3.25494</v>
+        <v>3.38832</v>
       </c>
       <c r="N41">
-        <v>22.02283777777778</v>
+        <v>21.88945777777778</v>
       </c>
       <c r="O41">
-        <v>4.845024311111111</v>
+        <v>4.815680711111111</v>
       </c>
       <c r="P41">
-        <v>17.17781346666667</v>
+        <v>17.07377706666667</v>
       </c>
       <c r="Q41">
-        <v>25.67781346666667</v>
+        <v>25.57377706666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1333868841054147</v>
+        <v>0.1346323768787361</v>
       </c>
       <c r="T41">
-        <v>1.274495885106239</v>
+        <v>1.292619322544853</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.765973498060726</v>
+        <v>7.460268740195075</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09772102612724165</v>
+        <v>0.09755799295018032</v>
       </c>
       <c r="C42">
-        <v>112.2667119167094</v>
+        <v>111.2033483489864</v>
       </c>
       <c r="D42">
-        <v>157.6667119167094</v>
+        <v>158.1633483489864</v>
       </c>
       <c r="E42">
-        <v>0.4000000000000128</v>
+        <v>1.960000000000015</v>
       </c>
       <c r="F42">
-        <v>62.40000000000001</v>
+        <v>63.96000000000001</v>
       </c>
       <c r="G42">
         <v>17</v>
@@ -4731,28 +4731,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M42">
-        <v>3.38832</v>
+        <v>3.473028000000001</v>
       </c>
       <c r="N42">
-        <v>21.88945777777778</v>
+        <v>21.80474977777778</v>
       </c>
       <c r="O42">
-        <v>4.815680711111111</v>
+        <v>4.797044951111111</v>
       </c>
       <c r="P42">
-        <v>17.07377706666667</v>
+        <v>17.00770482666667</v>
       </c>
       <c r="Q42">
-        <v>25.57377706666667</v>
+        <v>25.50770482666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1346323768787361</v>
+        <v>0.1359200897460683</v>
       </c>
       <c r="T42">
-        <v>1.292619322544853</v>
+        <v>1.311357113794946</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.460268740195075</v>
+        <v>7.278310966043975</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09755799295018032</v>
+        <v>0.097394959773119</v>
       </c>
       <c r="C43">
-        <v>111.2033483489864</v>
+        <v>110.1431233907614</v>
       </c>
       <c r="D43">
-        <v>158.1633483489864</v>
+        <v>158.6631233907614</v>
       </c>
       <c r="E43">
-        <v>1.960000000000015</v>
+        <v>3.520000000000017</v>
       </c>
       <c r="F43">
-        <v>63.96000000000001</v>
+        <v>65.52000000000001</v>
       </c>
       <c r="G43">
         <v>17</v>
@@ -4813,28 +4813,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M43">
-        <v>3.473028000000001</v>
+        <v>3.557736000000001</v>
       </c>
       <c r="N43">
-        <v>21.80474977777778</v>
+        <v>21.72004177777778</v>
       </c>
       <c r="O43">
-        <v>4.797044951111111</v>
+        <v>4.778409191111111</v>
       </c>
       <c r="P43">
-        <v>17.00770482666667</v>
+        <v>16.94163258666666</v>
       </c>
       <c r="Q43">
-        <v>25.50770482666667</v>
+        <v>25.44163258666666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1359200897460683</v>
+        <v>0.1372522065053776</v>
       </c>
       <c r="T43">
-        <v>1.311357113794946</v>
+        <v>1.3307410357778</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.278310966043975</v>
+        <v>7.105017847804832</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09739495977311902</v>
+        <v>0.09723192659605767</v>
       </c>
       <c r="C44">
-        <v>110.1431233907614</v>
+        <v>109.0860668891069</v>
       </c>
       <c r="D44">
-        <v>158.6631233907614</v>
+        <v>159.1660668891069</v>
       </c>
       <c r="E44">
-        <v>3.520000000000003</v>
+        <v>5.080000000000005</v>
       </c>
       <c r="F44">
-        <v>65.52</v>
+        <v>67.08</v>
       </c>
       <c r="G44">
         <v>17</v>
@@ -4895,28 +4895,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M44">
-        <v>3.557736</v>
+        <v>3.642444</v>
       </c>
       <c r="N44">
-        <v>21.72004177777778</v>
+        <v>21.63533377777778</v>
       </c>
       <c r="O44">
-        <v>4.778409191111112</v>
+        <v>4.759773431111111</v>
       </c>
       <c r="P44">
-        <v>16.94163258666667</v>
+        <v>16.87556034666667</v>
       </c>
       <c r="Q44">
-        <v>25.44163258666667</v>
+        <v>25.37556034666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1372522065053776</v>
+        <v>0.1386310642036099</v>
       </c>
       <c r="T44">
-        <v>1.3307410357778</v>
+        <v>1.350805095374088</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.105017847804834</v>
+        <v>6.93978487460007</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09723192659605767</v>
+        <v>0.09706889341899635</v>
       </c>
       <c r="C45">
-        <v>109.0860668891069</v>
+        <v>108.0322090707455</v>
       </c>
       <c r="D45">
-        <v>159.1660668891069</v>
+        <v>159.6722090707455</v>
       </c>
       <c r="E45">
-        <v>5.080000000000005</v>
+        <v>6.640000000000008</v>
       </c>
       <c r="F45">
-        <v>67.08</v>
+        <v>68.64</v>
       </c>
       <c r="G45">
         <v>17</v>
@@ -4977,28 +4977,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M45">
-        <v>3.642444</v>
+        <v>3.727152</v>
       </c>
       <c r="N45">
-        <v>21.63533377777778</v>
+        <v>21.55062577777778</v>
       </c>
       <c r="O45">
-        <v>4.759773431111111</v>
+        <v>4.741137671111111</v>
       </c>
       <c r="P45">
-        <v>16.87556034666667</v>
+        <v>16.80948810666667</v>
       </c>
       <c r="Q45">
-        <v>25.37556034666667</v>
+        <v>25.30948810666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1386310642036099</v>
+        <v>0.1400591668196363</v>
       </c>
       <c r="T45">
-        <v>1.350805095374088</v>
+        <v>1.371585728527386</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.93978487460007</v>
+        <v>6.782062491086432</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09706889341899635</v>
+        <v>0.09690586024193502</v>
       </c>
       <c r="C46">
-        <v>108.0322090707455</v>
+        <v>106.9815805481058</v>
       </c>
       <c r="D46">
-        <v>159.6722090707455</v>
+        <v>160.1815805481058</v>
       </c>
       <c r="E46">
-        <v>6.640000000000008</v>
+        <v>8.20000000000001</v>
       </c>
       <c r="F46">
-        <v>68.64</v>
+        <v>70.2</v>
       </c>
       <c r="G46">
         <v>17</v>
@@ -5059,28 +5059,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M46">
-        <v>3.727152</v>
+        <v>3.81186</v>
       </c>
       <c r="N46">
-        <v>21.55062577777778</v>
+        <v>21.46591777777778</v>
       </c>
       <c r="O46">
-        <v>4.741137671111111</v>
+        <v>4.722501911111111</v>
       </c>
       <c r="P46">
-        <v>16.80948810666667</v>
+        <v>16.74341586666667</v>
       </c>
       <c r="Q46">
-        <v>25.30948810666667</v>
+        <v>25.24341586666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1400591668196363</v>
+        <v>0.1415392004398819</v>
       </c>
       <c r="T46">
-        <v>1.371585728527386</v>
+        <v>1.393122021068077</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.782062491086432</v>
+        <v>6.631349991284512</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09690586024193502</v>
+        <v>0.09674282706487368</v>
       </c>
       <c r="C47">
-        <v>106.9815805481058</v>
+        <v>105.9342123254944</v>
       </c>
       <c r="D47">
-        <v>160.1815805481058</v>
+        <v>160.6942123254944</v>
       </c>
       <c r="E47">
-        <v>8.20000000000001</v>
+        <v>9.760000000000012</v>
       </c>
       <c r="F47">
-        <v>70.2</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="G47">
         <v>17</v>
@@ -5141,28 +5141,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M47">
-        <v>3.81186</v>
+        <v>3.896568</v>
       </c>
       <c r="N47">
-        <v>21.46591777777778</v>
+        <v>21.38120977777778</v>
       </c>
       <c r="O47">
-        <v>4.722501911111111</v>
+        <v>4.703866151111111</v>
       </c>
       <c r="P47">
-        <v>16.74341586666667</v>
+        <v>16.67734362666667</v>
       </c>
       <c r="Q47">
-        <v>25.24341586666667</v>
+        <v>25.17734362666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1415392004398819</v>
+        <v>0.1430740501201364</v>
       </c>
       <c r="T47">
-        <v>1.393122021068077</v>
+        <v>1.415455954073238</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.631349991284512</v>
+        <v>6.487190208865282</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09674282706487368</v>
+        <v>0.09657979388781236</v>
       </c>
       <c r="C48">
-        <v>105.9342123254944</v>
+        <v>104.8901358053862</v>
       </c>
       <c r="D48">
-        <v>160.6942123254944</v>
+        <v>161.2101358053862</v>
       </c>
       <c r="E48">
-        <v>9.760000000000012</v>
+        <v>11.32000000000001</v>
       </c>
       <c r="F48">
-        <v>71.76000000000001</v>
+        <v>73.32000000000001</v>
       </c>
       <c r="G48">
         <v>17</v>
@@ -5223,28 +5223,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M48">
-        <v>3.896568</v>
+        <v>3.981276</v>
       </c>
       <c r="N48">
-        <v>21.38120977777778</v>
+        <v>21.29650177777778</v>
       </c>
       <c r="O48">
-        <v>4.703866151111111</v>
+        <v>4.685230391111111</v>
       </c>
       <c r="P48">
-        <v>16.67734362666667</v>
+        <v>16.61127138666667</v>
       </c>
       <c r="Q48">
-        <v>25.17734362666667</v>
+        <v>25.11127138666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1430740501201364</v>
+        <v>0.1446668186562497</v>
       </c>
       <c r="T48">
-        <v>1.415455954073238</v>
+        <v>1.438632677003122</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.487190208865282</v>
+        <v>6.349164885272404</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09657979388781236</v>
+        <v>0.09641676071075103</v>
       </c>
       <c r="C49">
-        <v>104.8901358053862</v>
+        <v>103.8493827948376</v>
       </c>
       <c r="D49">
-        <v>161.2101358053862</v>
+        <v>161.7293827948376</v>
       </c>
       <c r="E49">
-        <v>11.32000000000001</v>
+        <v>12.88000000000002</v>
       </c>
       <c r="F49">
-        <v>73.32000000000001</v>
+        <v>74.88000000000001</v>
       </c>
       <c r="G49">
         <v>17</v>
@@ -5305,28 +5305,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M49">
-        <v>3.981276</v>
+        <v>4.065984</v>
       </c>
       <c r="N49">
-        <v>21.29650177777778</v>
+        <v>21.21179377777778</v>
       </c>
       <c r="O49">
-        <v>4.685230391111111</v>
+        <v>4.666594631111111</v>
       </c>
       <c r="P49">
-        <v>16.61127138666667</v>
+        <v>16.54519914666667</v>
       </c>
       <c r="Q49">
-        <v>25.11127138666667</v>
+        <v>25.04519914666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1446668186562497</v>
+        <v>0.1463208475206751</v>
       </c>
       <c r="T49">
-        <v>1.438632677003122</v>
+        <v>1.462700812353386</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.349164885272404</v>
+        <v>6.216890616829229</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09641676071075102</v>
+        <v>0.0966359275336897</v>
       </c>
       <c r="C50">
-        <v>103.8493827948377</v>
+        <v>101.5921256241194</v>
       </c>
       <c r="D50">
-        <v>161.7293827948377</v>
+        <v>161.0321256241194</v>
       </c>
       <c r="E50">
-        <v>12.88</v>
+        <v>14.44</v>
       </c>
       <c r="F50">
-        <v>74.88</v>
+        <v>76.44</v>
       </c>
       <c r="G50">
         <v>17</v>
@@ -5387,45 +5387,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M50">
-        <v>4.065984</v>
+        <v>4.227132</v>
       </c>
       <c r="N50">
-        <v>21.21179377777778</v>
+        <v>21.05064577777778</v>
       </c>
       <c r="O50">
-        <v>4.666594631111111</v>
+        <v>4.631142071111111</v>
       </c>
       <c r="P50">
-        <v>16.54519914666667</v>
+        <v>16.41950370666667</v>
       </c>
       <c r="Q50">
-        <v>25.04519914666667</v>
+        <v>24.91950370666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.146320847520675</v>
+        <v>0.1480397402621367</v>
       </c>
       <c r="T50">
-        <v>1.462700812353386</v>
+        <v>1.487712796148759</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.216890616829229</v>
+        <v>5.979888439201278</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0966359275336897</v>
+        <v>0.09648069435662837</v>
       </c>
       <c r="C51">
-        <v>101.5921256241194</v>
+        <v>100.52536133817</v>
       </c>
       <c r="D51">
-        <v>161.0321256241194</v>
+        <v>161.52536133817</v>
       </c>
       <c r="E51">
-        <v>14.44</v>
+        <v>16.00000000000001</v>
       </c>
       <c r="F51">
-        <v>76.44</v>
+        <v>78</v>
       </c>
       <c r="G51">
         <v>17</v>
@@ -5469,28 +5469,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M51">
-        <v>4.227132</v>
+        <v>4.313400000000001</v>
       </c>
       <c r="N51">
-        <v>21.05064577777778</v>
+        <v>20.96437777777778</v>
       </c>
       <c r="O51">
-        <v>4.631142071111111</v>
+        <v>4.612163111111111</v>
       </c>
       <c r="P51">
-        <v>16.41950370666667</v>
+        <v>16.35221466666667</v>
       </c>
       <c r="Q51">
-        <v>24.91950370666667</v>
+        <v>24.85221466666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1480397402621367</v>
+        <v>0.1498273887132567</v>
       </c>
       <c r="T51">
-        <v>1.487712796148759</v>
+        <v>1.513725259295946</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.979888439201278</v>
+        <v>5.860290670417251</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09648069435662837</v>
+        <v>0.09632546117956704</v>
       </c>
       <c r="C52">
-        <v>100.52536133817</v>
+        <v>99.46162786263361</v>
       </c>
       <c r="D52">
-        <v>161.52536133817</v>
+        <v>162.0216278626336</v>
       </c>
       <c r="E52">
-        <v>16.00000000000001</v>
+        <v>17.56000000000001</v>
       </c>
       <c r="F52">
-        <v>78</v>
+        <v>79.56</v>
       </c>
       <c r="G52">
         <v>17</v>
@@ -5551,28 +5551,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M52">
-        <v>4.313400000000001</v>
+        <v>4.399668</v>
       </c>
       <c r="N52">
-        <v>20.96437777777778</v>
+        <v>20.87810977777778</v>
       </c>
       <c r="O52">
-        <v>4.612163111111111</v>
+        <v>4.593184151111112</v>
       </c>
       <c r="P52">
-        <v>16.35221466666667</v>
+        <v>16.28492562666667</v>
       </c>
       <c r="Q52">
-        <v>24.85221466666667</v>
+        <v>24.78492562666667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1498273887132567</v>
+        <v>0.1516880024072797</v>
       </c>
       <c r="T52">
-        <v>1.513725259295946</v>
+        <v>1.540799455632815</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.860290670417251</v>
+        <v>5.745383010212993</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09632546117956704</v>
+        <v>0.09617022800250571</v>
       </c>
       <c r="C53">
-        <v>99.46162786263361</v>
+        <v>98.40095321896339</v>
       </c>
       <c r="D53">
-        <v>162.0216278626336</v>
+        <v>162.5209532189634</v>
       </c>
       <c r="E53">
-        <v>17.56000000000001</v>
+        <v>19.12000000000001</v>
       </c>
       <c r="F53">
-        <v>79.56</v>
+        <v>81.12</v>
       </c>
       <c r="G53">
         <v>17</v>
@@ -5633,28 +5633,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M53">
-        <v>4.399668</v>
+        <v>4.485936000000001</v>
       </c>
       <c r="N53">
-        <v>20.87810977777778</v>
+        <v>20.79184177777778</v>
       </c>
       <c r="O53">
-        <v>4.593184151111112</v>
+        <v>4.574205191111111</v>
       </c>
       <c r="P53">
-        <v>16.28492562666667</v>
+        <v>16.21763658666666</v>
       </c>
       <c r="Q53">
-        <v>24.78492562666667</v>
+        <v>24.71763658666666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1516880024072797</v>
+        <v>0.1536261416718869</v>
       </c>
       <c r="T53">
-        <v>1.540799455632815</v>
+        <v>1.56900174348372</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.745383010212993</v>
+        <v>5.634894875401203</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09617022800250571</v>
+        <v>0.09601499482544437</v>
       </c>
       <c r="C54">
-        <v>98.40095321896339</v>
+        <v>97.34336577511155</v>
       </c>
       <c r="D54">
-        <v>162.5209532189634</v>
+        <v>163.0233657751116</v>
       </c>
       <c r="E54">
-        <v>19.12000000000001</v>
+        <v>20.68000000000001</v>
       </c>
       <c r="F54">
-        <v>81.12</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="G54">
         <v>17</v>
@@ -5715,28 +5715,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M54">
-        <v>4.485936000000001</v>
+        <v>4.572204</v>
       </c>
       <c r="N54">
-        <v>20.79184177777778</v>
+        <v>20.70557377777778</v>
       </c>
       <c r="O54">
-        <v>4.574205191111111</v>
+        <v>4.555226231111112</v>
       </c>
       <c r="P54">
-        <v>16.21763658666666</v>
+        <v>16.15034754666667</v>
       </c>
       <c r="Q54">
-        <v>24.71763658666666</v>
+        <v>24.65034754666667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1536261416718869</v>
+        <v>0.155646754947754</v>
       </c>
       <c r="T54">
-        <v>1.56900174348372</v>
+        <v>1.598404128689982</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.634894875401203</v>
+        <v>5.52857610416722</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09601499482544437</v>
+        <v>0.09585976164838306</v>
       </c>
       <c r="C55">
-        <v>97.34336577511155</v>
+        <v>96.28889425090117</v>
       </c>
       <c r="D55">
-        <v>163.0233657751116</v>
+        <v>163.5288942509012</v>
       </c>
       <c r="E55">
-        <v>20.68000000000001</v>
+        <v>22.24000000000002</v>
       </c>
       <c r="F55">
-        <v>82.68000000000001</v>
+        <v>84.24000000000001</v>
       </c>
       <c r="G55">
         <v>17</v>
@@ -5797,28 +5797,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M55">
-        <v>4.572204</v>
+        <v>4.658472000000001</v>
       </c>
       <c r="N55">
-        <v>20.70557377777778</v>
+        <v>20.61930577777778</v>
       </c>
       <c r="O55">
-        <v>4.555226231111112</v>
+        <v>4.536247271111112</v>
       </c>
       <c r="P55">
-        <v>16.15034754666667</v>
+        <v>16.08305850666667</v>
       </c>
       <c r="Q55">
-        <v>24.65034754666667</v>
+        <v>24.58305850666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.155646754947754</v>
+        <v>0.1577552209747458</v>
       </c>
       <c r="T55">
-        <v>1.598404128689982</v>
+        <v>1.62908487847043</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.52857610416722</v>
+        <v>5.42619506520116</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09585976164838306</v>
+        <v>0.09570452847132171</v>
       </c>
       <c r="C56">
-        <v>96.28889425090117</v>
+        <v>95.23756772349961</v>
       </c>
       <c r="D56">
-        <v>163.5288942509012</v>
+        <v>164.0375677234996</v>
       </c>
       <c r="E56">
-        <v>22.24000000000002</v>
+        <v>23.80000000000002</v>
       </c>
       <c r="F56">
-        <v>84.24000000000001</v>
+        <v>85.80000000000001</v>
       </c>
       <c r="G56">
         <v>17</v>
@@ -5879,28 +5879,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M56">
-        <v>4.658472000000001</v>
+        <v>4.744740000000001</v>
       </c>
       <c r="N56">
-        <v>20.61930577777778</v>
+        <v>20.53303777777778</v>
       </c>
       <c r="O56">
-        <v>4.536247271111112</v>
+        <v>4.517268311111112</v>
       </c>
       <c r="P56">
-        <v>16.08305850666667</v>
+        <v>16.01576946666667</v>
       </c>
       <c r="Q56">
-        <v>24.58305850666667</v>
+        <v>24.51576946666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1577552209747458</v>
+        <v>0.1599573966029372</v>
       </c>
       <c r="T56">
-        <v>1.62908487847043</v>
+        <v>1.661129217130008</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.42619506520116</v>
+        <v>5.327536973106593</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09570452847132171</v>
+        <v>0.0955492952942604</v>
       </c>
       <c r="C57">
-        <v>95.23756772349961</v>
+        <v>94.18941563299288</v>
       </c>
       <c r="D57">
-        <v>164.0375677234996</v>
+        <v>164.5494156329929</v>
       </c>
       <c r="E57">
-        <v>23.80000000000002</v>
+        <v>25.36000000000002</v>
       </c>
       <c r="F57">
-        <v>85.80000000000001</v>
+        <v>87.36000000000001</v>
       </c>
       <c r="G57">
         <v>17</v>
@@ -5961,28 +5961,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M57">
-        <v>4.744740000000001</v>
+        <v>4.831008000000001</v>
       </c>
       <c r="N57">
-        <v>20.53303777777778</v>
+        <v>20.44676977777778</v>
       </c>
       <c r="O57">
-        <v>4.517268311111112</v>
+        <v>4.498289351111112</v>
       </c>
       <c r="P57">
-        <v>16.01576946666667</v>
+        <v>15.94848042666667</v>
       </c>
       <c r="Q57">
-        <v>24.51576946666667</v>
+        <v>24.44848042666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1599573966029372</v>
+        <v>0.1622596711233191</v>
       </c>
       <c r="T57">
-        <v>1.661129217130008</v>
+        <v>1.69463011663775</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.327536973106593</v>
+        <v>5.232402384301118</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0955492952942604</v>
+        <v>0.09539406211719906</v>
       </c>
       <c r="C58">
-        <v>94.18941563299288</v>
+        <v>93.14446778806607</v>
       </c>
       <c r="D58">
-        <v>164.5494156329929</v>
+        <v>165.0644677880661</v>
       </c>
       <c r="E58">
-        <v>25.36000000000002</v>
+        <v>26.92000000000002</v>
       </c>
       <c r="F58">
-        <v>87.36000000000001</v>
+        <v>88.92000000000002</v>
       </c>
       <c r="G58">
         <v>17</v>
@@ -6043,28 +6043,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M58">
-        <v>4.831008000000001</v>
+        <v>4.917276000000001</v>
       </c>
       <c r="N58">
-        <v>20.44676977777778</v>
+        <v>20.36050177777778</v>
       </c>
       <c r="O58">
-        <v>4.498289351111112</v>
+        <v>4.479310391111111</v>
       </c>
       <c r="P58">
-        <v>15.94848042666667</v>
+        <v>15.88119138666667</v>
       </c>
       <c r="Q58">
-        <v>24.44848042666667</v>
+        <v>24.38119138666666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1622596711233191</v>
+        <v>0.1646690281795327</v>
       </c>
       <c r="T58">
-        <v>1.69463011663775</v>
+        <v>1.729689197517944</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.232402384301118</v>
+        <v>5.140605851243203</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09539406211719906</v>
+        <v>0.09523882894013774</v>
       </c>
       <c r="C59">
-        <v>93.14446778806607</v>
+        <v>92.10275437178959</v>
       </c>
       <c r="D59">
-        <v>165.0644677880661</v>
+        <v>165.5827543717896</v>
       </c>
       <c r="E59">
-        <v>26.92000000000002</v>
+        <v>28.48000000000003</v>
       </c>
       <c r="F59">
-        <v>88.92000000000002</v>
+        <v>90.48000000000002</v>
       </c>
       <c r="G59">
         <v>17</v>
@@ -6125,28 +6125,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M59">
-        <v>4.917276000000001</v>
+        <v>5.003544000000002</v>
       </c>
       <c r="N59">
-        <v>20.36050177777778</v>
+        <v>20.27423377777778</v>
       </c>
       <c r="O59">
-        <v>4.479310391111111</v>
+        <v>4.460331431111111</v>
       </c>
       <c r="P59">
-        <v>15.88119138666667</v>
+        <v>15.81390234666667</v>
       </c>
       <c r="Q59">
-        <v>24.38119138666666</v>
+        <v>24.31390234666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1646690281795327</v>
+        <v>0.1671931165241375</v>
       </c>
       <c r="T59">
-        <v>1.729689197517944</v>
+        <v>1.766417758440053</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.140605851243203</v>
+        <v>5.05197471587694</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09523882894013774</v>
+        <v>0.09508359576307643</v>
       </c>
       <c r="C60">
-        <v>92.10275437178962</v>
+        <v>91.06430594751606</v>
       </c>
       <c r="D60">
-        <v>165.5827543717896</v>
+        <v>166.1043059475161</v>
       </c>
       <c r="E60">
-        <v>28.48</v>
+        <v>30.04</v>
       </c>
       <c r="F60">
-        <v>90.47999999999999</v>
+        <v>92.03999999999999</v>
       </c>
       <c r="G60">
         <v>17</v>
@@ -6207,28 +6207,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M60">
-        <v>5.003544</v>
+        <v>5.089811999999999</v>
       </c>
       <c r="N60">
-        <v>20.27423377777778</v>
+        <v>20.18796577777778</v>
       </c>
       <c r="O60">
-        <v>4.460331431111112</v>
+        <v>4.441352471111112</v>
       </c>
       <c r="P60">
-        <v>15.81390234666667</v>
+        <v>15.74661330666667</v>
       </c>
       <c r="Q60">
-        <v>24.31390234666667</v>
+        <v>24.24661330666667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1671931165241375</v>
+        <v>0.1698403311294547</v>
       </c>
       <c r="T60">
-        <v>1.766417758440053</v>
+        <v>1.804937956480313</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.051974715876943</v>
+        <v>4.966348025777334</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09508359576307643</v>
+        <v>0.09492836258601509</v>
       </c>
       <c r="C61">
-        <v>91.06430594751606</v>
+        <v>90.02915346488766</v>
       </c>
       <c r="D61">
-        <v>166.1043059475161</v>
+        <v>166.6291534648877</v>
       </c>
       <c r="E61">
-        <v>30.04</v>
+        <v>31.6</v>
       </c>
       <c r="F61">
-        <v>92.03999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G61">
         <v>17</v>
@@ -6289,28 +6289,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M61">
-        <v>5.089811999999999</v>
+        <v>5.17608</v>
       </c>
       <c r="N61">
-        <v>20.18796577777778</v>
+        <v>20.10169777777778</v>
       </c>
       <c r="O61">
-        <v>4.441352471111112</v>
+        <v>4.422373511111112</v>
       </c>
       <c r="P61">
-        <v>15.74661330666667</v>
+        <v>15.67932426666667</v>
       </c>
       <c r="Q61">
-        <v>24.24661330666667</v>
+        <v>24.17932426666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1698403311294547</v>
+        <v>0.1726199064650377</v>
       </c>
       <c r="T61">
-        <v>1.804937956480313</v>
+        <v>1.845384164422586</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.966348025777334</v>
+        <v>4.883575558681045</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09492836258601509</v>
+        <v>0.09477312940895376</v>
       </c>
       <c r="C62">
-        <v>90.02915346488766</v>
+        <v>88.99732826595854</v>
       </c>
       <c r="D62">
-        <v>166.6291534648877</v>
+        <v>167.1573282659585</v>
       </c>
       <c r="E62">
-        <v>31.6</v>
+        <v>33.16</v>
       </c>
       <c r="F62">
-        <v>93.59999999999999</v>
+        <v>95.16</v>
       </c>
       <c r="G62">
         <v>17</v>
@@ -6371,28 +6371,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M62">
-        <v>5.17608</v>
+        <v>5.262348</v>
       </c>
       <c r="N62">
-        <v>20.10169777777778</v>
+        <v>20.01542977777778</v>
       </c>
       <c r="O62">
-        <v>4.422373511111112</v>
+        <v>4.403394551111112</v>
       </c>
       <c r="P62">
-        <v>15.67932426666667</v>
+        <v>15.61203522666667</v>
       </c>
       <c r="Q62">
-        <v>24.17932426666667</v>
+        <v>24.11203522666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1726199064650377</v>
+        <v>0.1755420241255224</v>
       </c>
       <c r="T62">
-        <v>1.845384164422586</v>
+        <v>1.887904536874719</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.883575558681045</v>
+        <v>4.803516942964961</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09477312940895376</v>
+        <v>0.09461789623189243</v>
       </c>
       <c r="C63">
-        <v>88.99732826595854</v>
+        <v>87.96886209143415</v>
       </c>
       <c r="D63">
-        <v>167.1573282659585</v>
+        <v>167.6888620914341</v>
       </c>
       <c r="E63">
-        <v>33.16</v>
+        <v>34.72000000000001</v>
       </c>
       <c r="F63">
-        <v>95.16</v>
+        <v>96.72</v>
       </c>
       <c r="G63">
         <v>17</v>
@@ -6453,28 +6453,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M63">
-        <v>5.262348</v>
+        <v>5.348616</v>
       </c>
       <c r="N63">
-        <v>20.01542977777778</v>
+        <v>19.92916177777778</v>
       </c>
       <c r="O63">
-        <v>4.403394551111112</v>
+        <v>4.384415591111112</v>
       </c>
       <c r="P63">
-        <v>15.61203522666667</v>
+        <v>15.54474618666667</v>
       </c>
       <c r="Q63">
-        <v>24.11203522666667</v>
+        <v>24.04474618666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1755420241255224</v>
+        <v>0.1786179374523485</v>
       </c>
       <c r="T63">
-        <v>1.887904536874719</v>
+        <v>1.932662823666439</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.803516942964961</v>
+        <v>4.726040863239721</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09461789623189243</v>
+        <v>0.0944626630548311</v>
       </c>
       <c r="C64">
-        <v>87.96886209143415</v>
+        <v>86.94378708702925</v>
       </c>
       <c r="D64">
-        <v>167.6888620914341</v>
+        <v>168.2237870870293</v>
       </c>
       <c r="E64">
-        <v>34.72000000000001</v>
+        <v>36.28000000000001</v>
       </c>
       <c r="F64">
-        <v>96.72</v>
+        <v>98.28</v>
       </c>
       <c r="G64">
         <v>17</v>
@@ -6535,28 +6535,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M64">
-        <v>5.348616</v>
+        <v>5.434884</v>
       </c>
       <c r="N64">
-        <v>19.92916177777778</v>
+        <v>19.84289377777778</v>
       </c>
       <c r="O64">
-        <v>4.384415591111112</v>
+        <v>4.365436631111112</v>
       </c>
       <c r="P64">
-        <v>15.54474618666667</v>
+        <v>15.47745714666667</v>
       </c>
       <c r="Q64">
-        <v>24.04474618666667</v>
+        <v>23.97745714666667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1786179374523485</v>
+        <v>0.1818601163644084</v>
       </c>
       <c r="T64">
-        <v>1.932662823666439</v>
+        <v>1.979840477311764</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.726040863239721</v>
+        <v>4.651024341600994</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0944626630548311</v>
+        <v>0.09430742987776977</v>
       </c>
       <c r="C65">
-        <v>86.94378708702925</v>
+        <v>85.92213580994883</v>
       </c>
       <c r="D65">
-        <v>168.2237870870293</v>
+        <v>168.7621358099488</v>
       </c>
       <c r="E65">
-        <v>36.28000000000001</v>
+        <v>37.84000000000001</v>
       </c>
       <c r="F65">
-        <v>98.28</v>
+        <v>99.84</v>
       </c>
       <c r="G65">
         <v>17</v>
@@ -6617,28 +6617,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M65">
-        <v>5.434884</v>
+        <v>5.521152000000001</v>
       </c>
       <c r="N65">
-        <v>19.84289377777778</v>
+        <v>19.75662577777778</v>
       </c>
       <c r="O65">
-        <v>4.365436631111112</v>
+        <v>4.346457671111112</v>
       </c>
       <c r="P65">
-        <v>15.47745714666667</v>
+        <v>15.41016810666667</v>
       </c>
       <c r="Q65">
-        <v>23.97745714666667</v>
+        <v>23.91016810666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1818601163644084</v>
+        <v>0.1852824163271382</v>
       </c>
       <c r="T65">
-        <v>1.979840477311764</v>
+        <v>2.029639111715164</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.651024341600994</v>
+        <v>4.578352086263479</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09430742987776977</v>
+        <v>0.09415219670070844</v>
       </c>
       <c r="C66">
-        <v>85.92213580994883</v>
+        <v>84.90394123549322</v>
       </c>
       <c r="D66">
-        <v>168.7621358099488</v>
+        <v>169.3039412354932</v>
       </c>
       <c r="E66">
-        <v>37.84000000000001</v>
+        <v>39.40000000000001</v>
       </c>
       <c r="F66">
-        <v>99.84</v>
+        <v>101.4</v>
       </c>
       <c r="G66">
         <v>17</v>
@@ -6699,28 +6699,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M66">
-        <v>5.521152000000001</v>
+        <v>5.60742</v>
       </c>
       <c r="N66">
-        <v>19.75662577777778</v>
+        <v>19.67035777777778</v>
       </c>
       <c r="O66">
-        <v>4.346457671111112</v>
+        <v>4.327478711111111</v>
       </c>
       <c r="P66">
-        <v>15.41016810666667</v>
+        <v>15.34287906666667</v>
       </c>
       <c r="Q66">
-        <v>23.91016810666667</v>
+        <v>23.84287906666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1852824163271382</v>
+        <v>0.1889002762877384</v>
       </c>
       <c r="T66">
-        <v>2.029639111715164</v>
+        <v>2.082283382370186</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.578352086263479</v>
+        <v>4.507915900320963</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09415219670070844</v>
+        <v>0.09528396352364712</v>
       </c>
       <c r="C67">
-        <v>84.90394123549322</v>
+        <v>79.47172547024789</v>
       </c>
       <c r="D67">
-        <v>169.3039412354932</v>
+        <v>165.4317254702479</v>
       </c>
       <c r="E67">
-        <v>39.40000000000001</v>
+        <v>40.96000000000002</v>
       </c>
       <c r="F67">
-        <v>101.4</v>
+        <v>102.96</v>
       </c>
       <c r="G67">
         <v>17</v>
@@ -6781,45 +6781,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M67">
-        <v>5.60742</v>
+        <v>5.951088000000001</v>
       </c>
       <c r="N67">
-        <v>19.67035777777778</v>
+        <v>19.32668977777778</v>
       </c>
       <c r="O67">
-        <v>4.327478711111111</v>
+        <v>4.251871751111111</v>
       </c>
       <c r="P67">
-        <v>15.34287906666667</v>
+        <v>15.07481802666667</v>
       </c>
       <c r="Q67">
-        <v>23.84287906666667</v>
+        <v>23.57481802666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1889002762877384</v>
+        <v>0.1927309515401386</v>
       </c>
       <c r="T67">
-        <v>2.082283382370186</v>
+        <v>2.138024374828445</v>
       </c>
       <c r="U67">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.507915900320963</v>
+        <v>4.24758931102645</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09528396352364712</v>
+        <v>0.09514823034658577</v>
       </c>
       <c r="C68">
-        <v>79.47172547024789</v>
+        <v>78.36674834598452</v>
       </c>
       <c r="D68">
-        <v>165.4317254702479</v>
+        <v>165.8867483459845</v>
       </c>
       <c r="E68">
-        <v>40.96000000000002</v>
+        <v>42.52000000000002</v>
       </c>
       <c r="F68">
-        <v>102.96</v>
+        <v>104.52</v>
       </c>
       <c r="G68">
         <v>17</v>
@@ -6863,28 +6863,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M68">
-        <v>5.951088000000001</v>
+        <v>6.041256000000001</v>
       </c>
       <c r="N68">
-        <v>19.32668977777778</v>
+        <v>19.23652177777778</v>
       </c>
       <c r="O68">
-        <v>4.251871751111111</v>
+        <v>4.232034791111111</v>
       </c>
       <c r="P68">
-        <v>15.07481802666667</v>
+        <v>15.00448698666667</v>
       </c>
       <c r="Q68">
-        <v>23.57481802666667</v>
+        <v>23.50448698666667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1927309515401386</v>
+        <v>0.1967937889290478</v>
       </c>
       <c r="T68">
-        <v>2.138024374828445</v>
+        <v>2.197143609253871</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.24758931102645</v>
+        <v>4.184192455637996</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09514823034658577</v>
+        <v>0.09501249716952447</v>
       </c>
       <c r="C69">
-        <v>78.36674834598452</v>
+        <v>77.26428122239614</v>
       </c>
       <c r="D69">
-        <v>165.8867483459845</v>
+        <v>166.3442812223961</v>
       </c>
       <c r="E69">
-        <v>42.52000000000002</v>
+        <v>44.08000000000002</v>
       </c>
       <c r="F69">
-        <v>104.52</v>
+        <v>106.08</v>
       </c>
       <c r="G69">
         <v>17</v>
@@ -6945,28 +6945,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M69">
-        <v>6.041256000000001</v>
+        <v>6.131424000000001</v>
       </c>
       <c r="N69">
-        <v>19.23652177777778</v>
+        <v>19.14635377777778</v>
       </c>
       <c r="O69">
-        <v>4.232034791111111</v>
+        <v>4.21219783111111</v>
       </c>
       <c r="P69">
-        <v>15.00448698666667</v>
+        <v>14.93415594666667</v>
       </c>
       <c r="Q69">
-        <v>23.50448698666667</v>
+        <v>23.43415594666666</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1967937889290478</v>
+        <v>0.201110553654764</v>
       </c>
       <c r="T69">
-        <v>2.197143609253871</v>
+        <v>2.259957795830887</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.184192455637996</v>
+        <v>4.122660213643319</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09501249716952447</v>
+        <v>0.09487676399246313</v>
       </c>
       <c r="C70">
-        <v>77.26428122239614</v>
+        <v>76.16434492545056</v>
       </c>
       <c r="D70">
-        <v>166.3442812223961</v>
+        <v>166.8043449254506</v>
       </c>
       <c r="E70">
-        <v>44.08000000000002</v>
+        <v>45.64000000000002</v>
       </c>
       <c r="F70">
-        <v>106.08</v>
+        <v>107.64</v>
       </c>
       <c r="G70">
         <v>17</v>
@@ -7027,28 +7027,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M70">
-        <v>6.131424000000001</v>
+        <v>6.221592000000001</v>
       </c>
       <c r="N70">
-        <v>19.14635377777778</v>
+        <v>19.05618577777778</v>
       </c>
       <c r="O70">
-        <v>4.21219783111111</v>
+        <v>4.192360871111111</v>
       </c>
       <c r="P70">
-        <v>14.93415594666667</v>
+        <v>14.86382490666667</v>
       </c>
       <c r="Q70">
-        <v>23.43415594666666</v>
+        <v>23.36382490666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.201110553654764</v>
+        <v>0.2057058193305262</v>
       </c>
       <c r="T70">
-        <v>2.259957795830887</v>
+        <v>2.326824510574161</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.122660213643319</v>
+        <v>4.062911514894865</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09487676399246313</v>
+        <v>0.09474103081540178</v>
       </c>
       <c r="C71">
-        <v>76.16434492545056</v>
+        <v>75.06696051215053</v>
       </c>
       <c r="D71">
-        <v>166.8043449254506</v>
+        <v>167.2669605121505</v>
       </c>
       <c r="E71">
-        <v>45.64000000000002</v>
+        <v>47.20000000000002</v>
       </c>
       <c r="F71">
-        <v>107.64</v>
+        <v>109.2</v>
       </c>
       <c r="G71">
         <v>17</v>
@@ -7109,28 +7109,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M71">
-        <v>6.221592000000001</v>
+        <v>6.311760000000001</v>
       </c>
       <c r="N71">
-        <v>19.05618577777778</v>
+        <v>18.96601777777778</v>
       </c>
       <c r="O71">
-        <v>4.192360871111111</v>
+        <v>4.172523911111111</v>
       </c>
       <c r="P71">
-        <v>14.86382490666667</v>
+        <v>14.79349386666667</v>
       </c>
       <c r="Q71">
-        <v>23.36382490666666</v>
+        <v>23.29349386666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2057058193305262</v>
+        <v>0.2106074360513393</v>
       </c>
       <c r="T71">
-        <v>2.326824510574161</v>
+        <v>2.398149006300319</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.062911514894865</v>
+        <v>4.004869921824939</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09474103081540178</v>
+        <v>0.09654359763834047</v>
       </c>
       <c r="C72">
-        <v>75.06696051215053</v>
+        <v>67.56512966795383</v>
       </c>
       <c r="D72">
-        <v>167.2669605121505</v>
+        <v>161.3251296679538</v>
       </c>
       <c r="E72">
-        <v>47.20000000000002</v>
+        <v>48.76000000000001</v>
       </c>
       <c r="F72">
-        <v>109.2</v>
+        <v>110.76</v>
       </c>
       <c r="G72">
         <v>17</v>
@@ -7191,45 +7191,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M72">
-        <v>6.311760000000001</v>
+        <v>6.789588</v>
       </c>
       <c r="N72">
-        <v>18.96601777777778</v>
+        <v>18.48818977777778</v>
       </c>
       <c r="O72">
-        <v>4.172523911111111</v>
+        <v>4.06740175111111</v>
       </c>
       <c r="P72">
-        <v>14.79349386666667</v>
+        <v>14.42078802666667</v>
       </c>
       <c r="Q72">
-        <v>23.29349386666667</v>
+        <v>22.92078802666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2106074360513393</v>
+        <v>0.2158470953046224</v>
       </c>
       <c r="T72">
-        <v>2.398149006300319</v>
+        <v>2.474392432766214</v>
       </c>
       <c r="U72">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.22</v>
       </c>
       <c r="W72">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.004869921824939</v>
+        <v>3.72302086338343</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09654359763834047</v>
+        <v>0.09643516446127914</v>
       </c>
       <c r="C73">
-        <v>67.56512966795384</v>
+        <v>66.35060097304071</v>
       </c>
       <c r="D73">
-        <v>161.3251296679538</v>
+        <v>161.6706009730407</v>
       </c>
       <c r="E73">
-        <v>48.76</v>
+        <v>50.32</v>
       </c>
       <c r="F73">
-        <v>110.76</v>
+        <v>112.32</v>
       </c>
       <c r="G73">
         <v>17</v>
@@ -7273,28 +7273,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M73">
-        <v>6.789587999999999</v>
+        <v>6.885216</v>
       </c>
       <c r="N73">
-        <v>18.48818977777778</v>
+        <v>18.39256177777778</v>
       </c>
       <c r="O73">
-        <v>4.067401751111111</v>
+        <v>4.046363591111112</v>
       </c>
       <c r="P73">
-        <v>14.42078802666667</v>
+        <v>14.34619818666667</v>
       </c>
       <c r="Q73">
-        <v>22.92078802666667</v>
+        <v>22.84619818666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2158470953046223</v>
+        <v>0.2214610159331398</v>
       </c>
       <c r="T73">
-        <v>2.474392432766213</v>
+        <v>2.556081818265386</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.723020863383431</v>
+        <v>3.671312240280883</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09643516446127914</v>
+        <v>0.09632673128421781</v>
       </c>
       <c r="C74">
-        <v>66.35060097304071</v>
+        <v>65.1375550794188</v>
       </c>
       <c r="D74">
-        <v>161.6706009730407</v>
+        <v>162.0175550794188</v>
       </c>
       <c r="E74">
-        <v>50.32</v>
+        <v>51.88</v>
       </c>
       <c r="F74">
-        <v>112.32</v>
+        <v>113.88</v>
       </c>
       <c r="G74">
         <v>17</v>
@@ -7355,28 +7355,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M74">
-        <v>6.885216</v>
+        <v>6.980843999999999</v>
       </c>
       <c r="N74">
-        <v>18.39256177777778</v>
+        <v>18.29693377777778</v>
       </c>
       <c r="O74">
-        <v>4.046363591111112</v>
+        <v>4.025325431111112</v>
       </c>
       <c r="P74">
-        <v>14.34619818666667</v>
+        <v>14.27160834666667</v>
       </c>
       <c r="Q74">
-        <v>22.84619818666667</v>
+        <v>22.77160834666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2214610159331398</v>
+        <v>0.22749078253414</v>
       </c>
       <c r="T74">
-        <v>2.556081818265386</v>
+        <v>2.643822269357089</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.671312240280883</v>
+        <v>3.621020291783885</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09632673128421781</v>
+        <v>0.09621829810715649</v>
       </c>
       <c r="C75">
-        <v>65.1375550794188</v>
+        <v>63.92600155414175</v>
       </c>
       <c r="D75">
-        <v>162.0175550794188</v>
+        <v>162.3660015541417</v>
       </c>
       <c r="E75">
-        <v>51.88</v>
+        <v>53.44</v>
       </c>
       <c r="F75">
-        <v>113.88</v>
+        <v>115.44</v>
       </c>
       <c r="G75">
         <v>17</v>
@@ -7437,28 +7437,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M75">
-        <v>6.980843999999999</v>
+        <v>7.076472</v>
       </c>
       <c r="N75">
-        <v>18.29693377777778</v>
+        <v>18.20130577777778</v>
       </c>
       <c r="O75">
-        <v>4.025325431111112</v>
+        <v>4.004287271111112</v>
       </c>
       <c r="P75">
-        <v>14.27160834666667</v>
+        <v>14.19701850666667</v>
       </c>
       <c r="Q75">
-        <v>22.77160834666667</v>
+        <v>22.69701850666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.22749078253414</v>
+        <v>0.2339843773352172</v>
       </c>
       <c r="T75">
-        <v>2.643822269357089</v>
+        <v>2.738311985917385</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.621020291783885</v>
+        <v>3.572087585138156</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09621829810715649</v>
+        <v>0.09610986493009516</v>
       </c>
       <c r="C76">
-        <v>63.92600155414175</v>
+        <v>62.71595004674302</v>
       </c>
       <c r="D76">
-        <v>162.3660015541417</v>
+        <v>162.715950046743</v>
       </c>
       <c r="E76">
-        <v>53.44</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="F76">
-        <v>115.44</v>
+        <v>117</v>
       </c>
       <c r="G76">
         <v>17</v>
@@ -7519,28 +7519,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M76">
-        <v>7.076472</v>
+        <v>7.1721</v>
       </c>
       <c r="N76">
-        <v>18.20130577777778</v>
+        <v>18.10567777777778</v>
       </c>
       <c r="O76">
-        <v>4.004287271111112</v>
+        <v>3.983249111111111</v>
       </c>
       <c r="P76">
-        <v>14.19701850666667</v>
+        <v>14.12242866666667</v>
       </c>
       <c r="Q76">
-        <v>22.69701850666667</v>
+        <v>22.62242866666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2339843773352172</v>
+        <v>0.2409974597203806</v>
       </c>
       <c r="T76">
-        <v>2.738311985917385</v>
+        <v>2.840360879802506</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.572087585138156</v>
+        <v>3.524459750669647</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09610986493009516</v>
+        <v>0.09766127175303382</v>
       </c>
       <c r="C77">
-        <v>62.71595004674302</v>
+        <v>56.28837494550774</v>
       </c>
       <c r="D77">
-        <v>162.715950046743</v>
+        <v>157.8483749455077</v>
       </c>
       <c r="E77">
-        <v>55.00000000000001</v>
+        <v>56.56000000000001</v>
       </c>
       <c r="F77">
-        <v>117</v>
+        <v>118.56</v>
       </c>
       <c r="G77">
         <v>17</v>
@@ -7601,45 +7601,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M77">
-        <v>7.1721</v>
+        <v>7.599696000000001</v>
       </c>
       <c r="N77">
-        <v>18.10567777777778</v>
+        <v>17.67808177777778</v>
       </c>
       <c r="O77">
-        <v>3.983249111111111</v>
+        <v>3.889177991111111</v>
       </c>
       <c r="P77">
-        <v>14.12242866666667</v>
+        <v>13.78890378666667</v>
       </c>
       <c r="Q77">
-        <v>22.62242866666667</v>
+        <v>22.28890378666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2409974597203806</v>
+        <v>0.2485949656376409</v>
       </c>
       <c r="T77">
-        <v>2.840360879802506</v>
+        <v>2.950913848178053</v>
       </c>
       <c r="U77">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.22</v>
       </c>
       <c r="W77">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.524459750669647</v>
+        <v>3.326156438070388</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09766127175303382</v>
+        <v>0.0975746785759725</v>
       </c>
       <c r="C78">
-        <v>56.28837494550774</v>
+        <v>54.9923764353565</v>
       </c>
       <c r="D78">
-        <v>157.8483749455077</v>
+        <v>158.1123764353565</v>
       </c>
       <c r="E78">
-        <v>56.56000000000001</v>
+        <v>58.12000000000001</v>
       </c>
       <c r="F78">
-        <v>118.56</v>
+        <v>120.12</v>
       </c>
       <c r="G78">
         <v>17</v>
@@ -7683,28 +7683,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M78">
-        <v>7.599696000000001</v>
+        <v>7.699692000000001</v>
       </c>
       <c r="N78">
-        <v>17.67808177777778</v>
+        <v>17.57808577777778</v>
       </c>
       <c r="O78">
-        <v>3.889177991111111</v>
+        <v>3.867178871111112</v>
       </c>
       <c r="P78">
-        <v>13.78890378666667</v>
+        <v>13.71090690666667</v>
       </c>
       <c r="Q78">
-        <v>22.28890378666667</v>
+        <v>22.21090690666667</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2485949656376409</v>
+        <v>0.2568531242433587</v>
       </c>
       <c r="T78">
-        <v>2.950913848178053</v>
+        <v>3.071080118151473</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.326156438070388</v>
+        <v>3.282959601212331</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0975746785759725</v>
+        <v>0.09748808539891118</v>
       </c>
       <c r="C79">
-        <v>54.9923764353565</v>
+        <v>53.69726248990054</v>
       </c>
       <c r="D79">
-        <v>158.1123764353565</v>
+        <v>158.3772624899005</v>
       </c>
       <c r="E79">
-        <v>58.12000000000001</v>
+        <v>59.68000000000001</v>
       </c>
       <c r="F79">
-        <v>120.12</v>
+        <v>121.68</v>
       </c>
       <c r="G79">
         <v>17</v>
@@ -7765,28 +7765,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M79">
-        <v>7.699692000000001</v>
+        <v>7.799688000000001</v>
       </c>
       <c r="N79">
-        <v>17.57808577777778</v>
+        <v>17.47808977777778</v>
       </c>
       <c r="O79">
-        <v>3.867178871111112</v>
+        <v>3.845179751111111</v>
       </c>
       <c r="P79">
-        <v>13.71090690666667</v>
+        <v>13.63291002666667</v>
       </c>
       <c r="Q79">
-        <v>22.21090690666667</v>
+        <v>22.13291002666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2568531242433587</v>
+        <v>0.2658620245405053</v>
       </c>
       <c r="T79">
-        <v>3.071080118151473</v>
+        <v>3.202170594486113</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.282959601212331</v>
+        <v>3.240870375555763</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09748808539891118</v>
+        <v>0.09740149222184985</v>
       </c>
       <c r="C80">
-        <v>53.69726248990054</v>
+        <v>52.40303756234059</v>
       </c>
       <c r="D80">
-        <v>158.3772624899005</v>
+        <v>158.6430375623406</v>
       </c>
       <c r="E80">
-        <v>59.68000000000001</v>
+        <v>61.24000000000002</v>
       </c>
       <c r="F80">
-        <v>121.68</v>
+        <v>123.24</v>
       </c>
       <c r="G80">
         <v>17</v>
@@ -7847,28 +7847,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M80">
-        <v>7.799688000000001</v>
+        <v>7.899684000000001</v>
       </c>
       <c r="N80">
-        <v>17.47808977777778</v>
+        <v>17.37809377777778</v>
       </c>
       <c r="O80">
-        <v>3.845179751111111</v>
+        <v>3.823180631111111</v>
       </c>
       <c r="P80">
-        <v>13.63291002666667</v>
+        <v>13.55491314666667</v>
       </c>
       <c r="Q80">
-        <v>22.13291002666667</v>
+        <v>22.05491314666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2658620245405053</v>
+        <v>0.2757289153421421</v>
       </c>
       <c r="T80">
-        <v>3.202170594486113</v>
+        <v>3.34574587809072</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.240870375555763</v>
+        <v>3.199846699915816</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09740149222184985</v>
+        <v>0.09731489904478852</v>
       </c>
       <c r="C81">
-        <v>52.40303756234059</v>
+        <v>51.10970613581949</v>
       </c>
       <c r="D81">
-        <v>158.6430375623406</v>
+        <v>158.9097061358195</v>
       </c>
       <c r="E81">
-        <v>61.24000000000002</v>
+        <v>62.80000000000002</v>
       </c>
       <c r="F81">
-        <v>123.24</v>
+        <v>124.8</v>
       </c>
       <c r="G81">
         <v>17</v>
@@ -7929,28 +7929,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M81">
-        <v>7.899684000000001</v>
+        <v>7.999680000000001</v>
       </c>
       <c r="N81">
-        <v>17.37809377777778</v>
+        <v>17.27809777777778</v>
       </c>
       <c r="O81">
-        <v>3.823180631111111</v>
+        <v>3.801181511111111</v>
       </c>
       <c r="P81">
-        <v>13.55491314666667</v>
+        <v>13.47691626666667</v>
       </c>
       <c r="Q81">
-        <v>22.05491314666667</v>
+        <v>21.97691626666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2757289153421421</v>
+        <v>0.2865824952239426</v>
       </c>
       <c r="T81">
-        <v>3.34574587809072</v>
+        <v>3.503678690055787</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.199846699915816</v>
+        <v>3.159848616166868</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09731489904478852</v>
+        <v>0.09722830586772718</v>
       </c>
       <c r="C82">
-        <v>51.10970613581949</v>
+        <v>49.81727272367436</v>
       </c>
       <c r="D82">
-        <v>158.9097061358195</v>
+        <v>159.1772727236744</v>
       </c>
       <c r="E82">
-        <v>62.80000000000002</v>
+        <v>64.36000000000001</v>
       </c>
       <c r="F82">
-        <v>124.8</v>
+        <v>126.36</v>
       </c>
       <c r="G82">
         <v>17</v>
@@ -8011,28 +8011,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M82">
-        <v>7.999680000000001</v>
+        <v>8.099676000000001</v>
       </c>
       <c r="N82">
-        <v>17.27809777777778</v>
+        <v>17.17810177777778</v>
       </c>
       <c r="O82">
-        <v>3.801181511111111</v>
+        <v>3.779182391111111</v>
       </c>
       <c r="P82">
-        <v>13.47691626666667</v>
+        <v>13.39891938666667</v>
       </c>
       <c r="Q82">
-        <v>21.97691626666667</v>
+        <v>21.89891938666667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2865824952239426</v>
+        <v>0.2985785571985642</v>
       </c>
       <c r="T82">
-        <v>3.503678690055787</v>
+        <v>3.678236008543492</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.159848616166868</v>
+        <v>3.120838139424068</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09722830586772718</v>
+        <v>0.09714171269066586</v>
       </c>
       <c r="C83">
-        <v>49.81727272367436</v>
+        <v>48.52574186969107</v>
       </c>
       <c r="D83">
-        <v>159.1772727236744</v>
+        <v>159.4457418696911</v>
       </c>
       <c r="E83">
-        <v>64.36000000000001</v>
+        <v>65.92000000000002</v>
       </c>
       <c r="F83">
-        <v>126.36</v>
+        <v>127.92</v>
       </c>
       <c r="G83">
         <v>17</v>
@@ -8093,28 +8093,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M83">
-        <v>8.099676000000001</v>
+        <v>8.199672000000001</v>
       </c>
       <c r="N83">
-        <v>17.17810177777778</v>
+        <v>17.07810577777778</v>
       </c>
       <c r="O83">
-        <v>3.779182391111111</v>
+        <v>3.757183271111111</v>
       </c>
       <c r="P83">
-        <v>13.39891938666667</v>
+        <v>13.32092250666667</v>
       </c>
       <c r="Q83">
-        <v>21.89891938666667</v>
+        <v>21.82092250666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2985785571985642</v>
+        <v>0.3119075149481437</v>
       </c>
       <c r="T83">
-        <v>3.678236008543492</v>
+        <v>3.872188584640942</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.120838139424068</v>
+        <v>3.082779137723774</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09714171269066586</v>
+        <v>0.09705511951360453</v>
       </c>
       <c r="C84">
-        <v>48.52574186969107</v>
+        <v>47.23511814836178</v>
       </c>
       <c r="D84">
-        <v>159.4457418696911</v>
+        <v>159.7151181483618</v>
       </c>
       <c r="E84">
-        <v>65.92000000000002</v>
+        <v>67.48000000000002</v>
       </c>
       <c r="F84">
-        <v>127.92</v>
+        <v>129.48</v>
       </c>
       <c r="G84">
         <v>17</v>
@@ -8175,28 +8175,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M84">
-        <v>8.199672000000001</v>
+        <v>8.299668000000002</v>
       </c>
       <c r="N84">
-        <v>17.07810577777778</v>
+        <v>16.97810977777777</v>
       </c>
       <c r="O84">
-        <v>3.757183271111111</v>
+        <v>3.735184151111111</v>
       </c>
       <c r="P84">
-        <v>13.32092250666667</v>
+        <v>13.24292562666666</v>
       </c>
       <c r="Q84">
-        <v>21.82092250666667</v>
+        <v>21.74292562666666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3119075149481437</v>
+        <v>0.3268045853741444</v>
       </c>
       <c r="T84">
-        <v>3.872188584640942</v>
+        <v>4.088959110867505</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.082779137723774</v>
+        <v>3.045637220401801</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09705511951360453</v>
+        <v>0.09696852633654321</v>
       </c>
       <c r="C85">
-        <v>47.23511814836178</v>
+        <v>45.94540616514436</v>
       </c>
       <c r="D85">
-        <v>159.7151181483618</v>
+        <v>159.9854061651444</v>
       </c>
       <c r="E85">
-        <v>67.48000000000002</v>
+        <v>69.04000000000002</v>
       </c>
       <c r="F85">
-        <v>129.48</v>
+        <v>131.04</v>
       </c>
       <c r="G85">
         <v>17</v>
@@ -8257,28 +8257,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M85">
-        <v>8.299668000000002</v>
+        <v>8.399664000000001</v>
       </c>
       <c r="N85">
-        <v>16.97810977777777</v>
+        <v>16.87811377777778</v>
       </c>
       <c r="O85">
-        <v>3.735184151111111</v>
+        <v>3.713185031111111</v>
       </c>
       <c r="P85">
-        <v>13.24292562666666</v>
+        <v>13.16492874666667</v>
       </c>
       <c r="Q85">
-        <v>21.74292562666666</v>
+        <v>21.66492874666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3268045853741444</v>
+        <v>0.3435637896033952</v>
       </c>
       <c r="T85">
-        <v>4.088959110867505</v>
+        <v>4.332825952872388</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.045637220401801</v>
+        <v>3.009379634444637</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09696852633654321</v>
+        <v>0.1020533331594819</v>
       </c>
       <c r="C86">
-        <v>45.94540616514439</v>
+        <v>29.92413179882672</v>
       </c>
       <c r="D86">
-        <v>159.9854061651444</v>
+        <v>145.5241317988267</v>
       </c>
       <c r="E86">
-        <v>69.03999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F86">
-        <v>131.04</v>
+        <v>132.6</v>
       </c>
       <c r="G86">
         <v>17</v>
@@ -8339,45 +8339,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M86">
-        <v>8.399664</v>
+        <v>9.533940000000001</v>
       </c>
       <c r="N86">
-        <v>16.87811377777778</v>
+        <v>15.74383777777778</v>
       </c>
       <c r="O86">
-        <v>3.713185031111111</v>
+        <v>3.463644311111111</v>
       </c>
       <c r="P86">
-        <v>13.16492874666667</v>
+        <v>12.28019346666667</v>
       </c>
       <c r="Q86">
-        <v>21.66492874666667</v>
+        <v>20.78019346666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.343563789603395</v>
+        <v>0.3625575543965458</v>
       </c>
       <c r="T86">
-        <v>4.332825952872385</v>
+        <v>4.609208373811252</v>
       </c>
       <c r="U86">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V86">
         <v>0.22</v>
       </c>
       <c r="W86">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.009379634444637</v>
+        <v>2.65134642946964</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1020533331594819</v>
+        <v>0.1020275799824205</v>
       </c>
       <c r="C87">
-        <v>29.92413179882672</v>
+        <v>28.43078429808216</v>
       </c>
       <c r="D87">
-        <v>145.5241317988267</v>
+        <v>145.5907842980822</v>
       </c>
       <c r="E87">
-        <v>70.59999999999999</v>
+        <v>72.16</v>
       </c>
       <c r="F87">
-        <v>132.6</v>
+        <v>134.16</v>
       </c>
       <c r="G87">
         <v>17</v>
@@ -8421,28 +8421,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M87">
-        <v>9.533940000000001</v>
+        <v>9.646104000000001</v>
       </c>
       <c r="N87">
-        <v>15.74383777777778</v>
+        <v>15.63167377777778</v>
       </c>
       <c r="O87">
-        <v>3.463644311111111</v>
+        <v>3.438968231111111</v>
       </c>
       <c r="P87">
-        <v>12.28019346666667</v>
+        <v>12.19270554666667</v>
       </c>
       <c r="Q87">
-        <v>20.78019346666667</v>
+        <v>20.69270554666667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3625575543965458</v>
+        <v>0.3842647141601467</v>
       </c>
       <c r="T87">
-        <v>4.609208373811252</v>
+        <v>4.925073997741385</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.65134642946964</v>
+        <v>2.620516819824644</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1020275799824205</v>
+        <v>0.1020018268053592</v>
       </c>
       <c r="C88">
-        <v>28.43078429808216</v>
+        <v>26.93749788124578</v>
       </c>
       <c r="D88">
-        <v>145.5907842980822</v>
+        <v>145.6574978812458</v>
       </c>
       <c r="E88">
-        <v>72.16</v>
+        <v>73.72</v>
       </c>
       <c r="F88">
-        <v>134.16</v>
+        <v>135.72</v>
       </c>
       <c r="G88">
         <v>17</v>
@@ -8503,28 +8503,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M88">
-        <v>9.646104000000001</v>
+        <v>9.758268000000001</v>
       </c>
       <c r="N88">
-        <v>15.63167377777778</v>
+        <v>15.51950977777778</v>
       </c>
       <c r="O88">
-        <v>3.438968231111111</v>
+        <v>3.414292151111111</v>
       </c>
       <c r="P88">
-        <v>12.19270554666667</v>
+        <v>12.10521762666667</v>
       </c>
       <c r="Q88">
-        <v>20.69270554666667</v>
+        <v>20.60521762666666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3842647141601467</v>
+        <v>0.4093114369643016</v>
       </c>
       <c r="T88">
-        <v>4.925073997741385</v>
+        <v>5.289534333045385</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.620516819824644</v>
+        <v>2.590395936838154</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1020018268053592</v>
+        <v>0.1019760736282979</v>
       </c>
       <c r="C89">
-        <v>26.93749788124578</v>
+        <v>25.44427263232691</v>
       </c>
       <c r="D89">
-        <v>145.6574978812458</v>
+        <v>145.7242726323269</v>
       </c>
       <c r="E89">
-        <v>73.72</v>
+        <v>75.28</v>
       </c>
       <c r="F89">
-        <v>135.72</v>
+        <v>137.28</v>
       </c>
       <c r="G89">
         <v>17</v>
@@ -8585,28 +8585,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M89">
-        <v>9.758268000000001</v>
+        <v>9.870432000000001</v>
       </c>
       <c r="N89">
-        <v>15.51950977777778</v>
+        <v>15.40734577777778</v>
       </c>
       <c r="O89">
-        <v>3.414292151111111</v>
+        <v>3.389616071111111</v>
       </c>
       <c r="P89">
-        <v>12.10521762666667</v>
+        <v>12.01772970666667</v>
       </c>
       <c r="Q89">
-        <v>20.60521762666666</v>
+        <v>20.51772970666667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4093114369643016</v>
+        <v>0.4385326135691491</v>
       </c>
       <c r="T89">
-        <v>5.289534333045385</v>
+        <v>5.714738057566719</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.590395936838154</v>
+        <v>2.560959619374084</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1019760736282979</v>
+        <v>0.1019503204512366</v>
       </c>
       <c r="C90">
-        <v>25.44427263232691</v>
+        <v>23.95110863548905</v>
       </c>
       <c r="D90">
-        <v>145.7242726323269</v>
+        <v>145.7911086354891</v>
       </c>
       <c r="E90">
-        <v>75.28</v>
+        <v>76.84</v>
       </c>
       <c r="F90">
-        <v>137.28</v>
+        <v>138.84</v>
       </c>
       <c r="G90">
         <v>17</v>
@@ -8667,28 +8667,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M90">
-        <v>9.870432000000001</v>
+        <v>9.982596000000001</v>
       </c>
       <c r="N90">
-        <v>15.40734577777778</v>
+        <v>15.29518177777778</v>
       </c>
       <c r="O90">
-        <v>3.389616071111111</v>
+        <v>3.364939991111111</v>
       </c>
       <c r="P90">
-        <v>12.01772970666667</v>
+        <v>11.93024178666667</v>
       </c>
       <c r="Q90">
-        <v>20.51772970666667</v>
+        <v>20.43024178666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4385326135691491</v>
+        <v>0.4730667313748778</v>
       </c>
       <c r="T90">
-        <v>5.714738057566719</v>
+        <v>6.21725155018284</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.560959619374084</v>
+        <v>2.532184792190106</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1019503204512366</v>
+        <v>0.1019245672741752</v>
       </c>
       <c r="C91">
-        <v>23.95110863548905</v>
+        <v>22.45800597505007</v>
       </c>
       <c r="D91">
-        <v>145.7911086354891</v>
+        <v>145.8580059750501</v>
       </c>
       <c r="E91">
-        <v>76.84</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F91">
-        <v>138.84</v>
+        <v>140.4</v>
       </c>
       <c r="G91">
         <v>17</v>
@@ -8749,28 +8749,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M91">
-        <v>9.982596000000001</v>
+        <v>10.09476</v>
       </c>
       <c r="N91">
-        <v>15.29518177777778</v>
+        <v>15.18301777777778</v>
       </c>
       <c r="O91">
-        <v>3.364939991111111</v>
+        <v>3.340263911111111</v>
       </c>
       <c r="P91">
-        <v>11.93024178666667</v>
+        <v>11.84275386666667</v>
       </c>
       <c r="Q91">
-        <v>20.43024178666667</v>
+        <v>20.34275386666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4730667313748778</v>
+        <v>0.5145076727417524</v>
       </c>
       <c r="T91">
-        <v>6.21725155018284</v>
+        <v>6.820267741322186</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.532184792190106</v>
+        <v>2.504049405610215</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1019245672741752</v>
+        <v>0.1046670340971139</v>
       </c>
       <c r="C92">
-        <v>22.45800597505007</v>
+        <v>14.10284891674374</v>
       </c>
       <c r="D92">
-        <v>145.8580059750501</v>
+        <v>139.0628489167437</v>
       </c>
       <c r="E92">
-        <v>78.40000000000001</v>
+        <v>79.96000000000001</v>
       </c>
       <c r="F92">
-        <v>140.4</v>
+        <v>141.96</v>
       </c>
       <c r="G92">
         <v>17</v>
@@ -8831,45 +8831,45 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M92">
-        <v>10.09476</v>
+        <v>10.760568</v>
       </c>
       <c r="N92">
-        <v>15.18301777777778</v>
+        <v>14.51720977777778</v>
       </c>
       <c r="O92">
-        <v>3.340263911111111</v>
+        <v>3.193786151111111</v>
       </c>
       <c r="P92">
-        <v>11.84275386666667</v>
+        <v>11.32342362666667</v>
       </c>
       <c r="Q92">
-        <v>20.34275386666667</v>
+        <v>19.82342362666667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5145076727417524</v>
+        <v>0.5651577121901545</v>
       </c>
       <c r="T92">
-        <v>6.820267741322186</v>
+        <v>7.557287530492498</v>
       </c>
       <c r="U92">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V92">
         <v>0.22</v>
       </c>
       <c r="W92">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.504049405610215</v>
+        <v>2.349111847792587</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1046670340971139</v>
+        <v>0.1046717009200526</v>
       </c>
       <c r="C93">
-        <v>14.10284891674374</v>
+        <v>12.53182525540728</v>
       </c>
       <c r="D93">
-        <v>139.0628489167437</v>
+        <v>139.0518252554073</v>
       </c>
       <c r="E93">
-        <v>79.96000000000001</v>
+        <v>81.52000000000001</v>
       </c>
       <c r="F93">
-        <v>141.96</v>
+        <v>143.52</v>
       </c>
       <c r="G93">
         <v>17</v>
@@ -8913,28 +8913,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M93">
-        <v>10.760568</v>
+        <v>10.878816</v>
       </c>
       <c r="N93">
-        <v>14.51720977777778</v>
+        <v>14.39896177777778</v>
       </c>
       <c r="O93">
-        <v>3.193786151111111</v>
+        <v>3.167771591111111</v>
       </c>
       <c r="P93">
-        <v>11.32342362666667</v>
+        <v>11.23119018666667</v>
       </c>
       <c r="Q93">
-        <v>19.82342362666667</v>
+        <v>19.73119018666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5651577121901545</v>
+        <v>0.6284702615006574</v>
       </c>
       <c r="T93">
-        <v>7.557287530492498</v>
+        <v>8.47856226695539</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.349111847792587</v>
+        <v>2.323578023360058</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1046717009200526</v>
+        <v>0.1046763677429912</v>
       </c>
       <c r="C94">
-        <v>12.53182525540728</v>
+        <v>10.96080334164728</v>
       </c>
       <c r="D94">
-        <v>139.0518252554073</v>
+        <v>139.0408033416473</v>
       </c>
       <c r="E94">
-        <v>81.52000000000001</v>
+        <v>83.08000000000001</v>
       </c>
       <c r="F94">
-        <v>143.52</v>
+        <v>145.08</v>
       </c>
       <c r="G94">
         <v>17</v>
@@ -8995,28 +8995,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M94">
-        <v>10.878816</v>
+        <v>10.997064</v>
       </c>
       <c r="N94">
-        <v>14.39896177777778</v>
+        <v>14.28071377777778</v>
       </c>
       <c r="O94">
-        <v>3.167771591111111</v>
+        <v>3.141757031111111</v>
       </c>
       <c r="P94">
-        <v>11.23119018666667</v>
+        <v>11.13895674666667</v>
       </c>
       <c r="Q94">
-        <v>19.73119018666667</v>
+        <v>19.63895674666666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6284702615006574</v>
+        <v>0.709872110614161</v>
       </c>
       <c r="T94">
-        <v>8.47856226695539</v>
+        <v>9.663058356693391</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.323578023360058</v>
+        <v>2.298593313431455</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1046763677429912</v>
+        <v>0.1046810345659299</v>
       </c>
       <c r="C95">
-        <v>10.96080334164728</v>
+        <v>9.389783175048137</v>
       </c>
       <c r="D95">
-        <v>139.0408033416473</v>
+        <v>139.0297831750482</v>
       </c>
       <c r="E95">
-        <v>83.08000000000001</v>
+        <v>84.64000000000001</v>
       </c>
       <c r="F95">
-        <v>145.08</v>
+        <v>146.64</v>
       </c>
       <c r="G95">
         <v>17</v>
@@ -9077,28 +9077,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M95">
-        <v>10.997064</v>
+        <v>11.115312</v>
       </c>
       <c r="N95">
-        <v>14.28071377777778</v>
+        <v>14.16246577777778</v>
       </c>
       <c r="O95">
-        <v>3.141757031111111</v>
+        <v>3.115742471111111</v>
       </c>
       <c r="P95">
-        <v>11.13895674666667</v>
+        <v>11.04672330666667</v>
       </c>
       <c r="Q95">
-        <v>19.63895674666666</v>
+        <v>19.54672330666667</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.709872110614161</v>
+        <v>0.8184079094321659</v>
       </c>
       <c r="T95">
-        <v>9.663058356693391</v>
+        <v>11.24238647634406</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.298593313431455</v>
+        <v>2.274140193075802</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1046810345659299</v>
+        <v>0.1046857013888686</v>
       </c>
       <c r="C96">
-        <v>9.389783175048137</v>
+        <v>7.818764755194479</v>
       </c>
       <c r="D96">
-        <v>139.0297831750482</v>
+        <v>139.0187647551945</v>
       </c>
       <c r="E96">
-        <v>84.64000000000001</v>
+        <v>86.20000000000002</v>
       </c>
       <c r="F96">
-        <v>146.64</v>
+        <v>148.2</v>
       </c>
       <c r="G96">
         <v>17</v>
@@ -9159,28 +9159,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M96">
-        <v>11.115312</v>
+        <v>11.23356</v>
       </c>
       <c r="N96">
-        <v>14.16246577777778</v>
+        <v>14.04421777777778</v>
       </c>
       <c r="O96">
-        <v>3.115742471111111</v>
+        <v>3.089727911111111</v>
       </c>
       <c r="P96">
-        <v>11.04672330666667</v>
+        <v>10.95448986666667</v>
       </c>
       <c r="Q96">
-        <v>19.54672330666667</v>
+        <v>19.45448986666667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8184079094321659</v>
+        <v>0.9703580277773729</v>
       </c>
       <c r="T96">
-        <v>11.24238647634406</v>
+        <v>13.453445843855</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.274140193075802</v>
+        <v>2.250201875253951</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1046857013888686</v>
+        <v>0.1046903682118073</v>
       </c>
       <c r="C97">
-        <v>7.818764755194479</v>
+        <v>6.247748081671034</v>
       </c>
       <c r="D97">
-        <v>139.0187647551945</v>
+        <v>139.0077480816711</v>
       </c>
       <c r="E97">
-        <v>86.20000000000002</v>
+        <v>87.76000000000002</v>
       </c>
       <c r="F97">
-        <v>148.2</v>
+        <v>149.76</v>
       </c>
       <c r="G97">
         <v>17</v>
@@ -9241,28 +9241,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M97">
-        <v>11.23356</v>
+        <v>11.351808</v>
       </c>
       <c r="N97">
-        <v>14.04421777777778</v>
+        <v>13.92596977777778</v>
       </c>
       <c r="O97">
-        <v>3.089727911111111</v>
+        <v>3.063713351111111</v>
       </c>
       <c r="P97">
-        <v>10.95448986666667</v>
+        <v>10.86225642666667</v>
       </c>
       <c r="Q97">
-        <v>19.45448986666667</v>
+        <v>19.36225642666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9703580277773729</v>
+        <v>1.198283205295184</v>
       </c>
       <c r="T97">
-        <v>13.453445843855</v>
+        <v>16.77003489512141</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.250201875253951</v>
+        <v>2.226762272386722</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1046903682118073</v>
+        <v>0.1046950350347459</v>
       </c>
       <c r="C98">
-        <v>6.247748081671034</v>
+        <v>4.676733154062646</v>
       </c>
       <c r="D98">
-        <v>139.007748081671</v>
+        <v>138.9967331540626</v>
       </c>
       <c r="E98">
-        <v>87.75999999999999</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="F98">
-        <v>149.76</v>
+        <v>151.32</v>
       </c>
       <c r="G98">
         <v>17</v>
@@ -9323,28 +9323,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M98">
-        <v>11.351808</v>
+        <v>11.470056</v>
       </c>
       <c r="N98">
-        <v>13.92596977777778</v>
+        <v>13.80772177777778</v>
       </c>
       <c r="O98">
-        <v>3.063713351111111</v>
+        <v>3.037698791111112</v>
       </c>
       <c r="P98">
-        <v>10.86225642666667</v>
+        <v>10.77002298666667</v>
       </c>
       <c r="Q98">
-        <v>19.36225642666667</v>
+        <v>19.27002298666667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.198283205295181</v>
+        <v>1.578158501158196</v>
       </c>
       <c r="T98">
-        <v>16.77003489512137</v>
+        <v>22.2976833138987</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.226762272386723</v>
+        <v>2.203805960300262</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1046950350347459</v>
+        <v>0.1046997018576846</v>
       </c>
       <c r="C99">
-        <v>4.676733154062646</v>
+        <v>3.105719971954329</v>
       </c>
       <c r="D99">
-        <v>138.9967331540626</v>
+        <v>138.9857199719543</v>
       </c>
       <c r="E99">
-        <v>89.31999999999999</v>
+        <v>90.88</v>
       </c>
       <c r="F99">
-        <v>151.32</v>
+        <v>152.88</v>
       </c>
       <c r="G99">
         <v>17</v>
@@ -9405,28 +9405,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M99">
-        <v>11.470056</v>
+        <v>11.588304</v>
       </c>
       <c r="N99">
-        <v>13.80772177777778</v>
+        <v>13.68947377777778</v>
       </c>
       <c r="O99">
-        <v>3.037698791111112</v>
+        <v>3.011684231111111</v>
       </c>
       <c r="P99">
-        <v>10.77002298666667</v>
+        <v>10.67778954666667</v>
       </c>
       <c r="Q99">
-        <v>19.27002298666667</v>
+        <v>19.17778954666667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.578158501158196</v>
+        <v>2.337909092884228</v>
       </c>
       <c r="T99">
-        <v>22.2976833138987</v>
+        <v>33.35298015145335</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.203805960300262</v>
+        <v>2.18131814437883</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1046997018576846</v>
+        <v>0.1047043686806233</v>
       </c>
       <c r="C100">
-        <v>3.105719971954329</v>
+        <v>1.534708534931212</v>
       </c>
       <c r="D100">
-        <v>138.9857199719543</v>
+        <v>138.9747085349312</v>
       </c>
       <c r="E100">
-        <v>90.88</v>
+        <v>92.44</v>
       </c>
       <c r="F100">
-        <v>152.88</v>
+        <v>154.44</v>
       </c>
       <c r="G100">
         <v>17</v>
@@ -9487,28 +9487,28 @@
         <v>25.27777777777778</v>
       </c>
       <c r="M100">
-        <v>11.588304</v>
+        <v>11.706552</v>
       </c>
       <c r="N100">
-        <v>13.68947377777778</v>
+        <v>13.57122577777778</v>
       </c>
       <c r="O100">
-        <v>3.011684231111111</v>
+        <v>2.985669671111111</v>
       </c>
       <c r="P100">
-        <v>10.67778954666667</v>
+        <v>10.58555610666667</v>
       </c>
       <c r="Q100">
-        <v>19.17778954666667</v>
+        <v>19.08555610666667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.337909092884228</v>
+        <v>4.617160868062324</v>
       </c>
       <c r="T100">
-        <v>33.35298015145335</v>
+        <v>66.51887066411732</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.18131814437883</v>
+        <v>2.159284627768943</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1047043686806233</v>
-      </c>
-      <c r="C101">
-        <v>1.534708534931212</v>
-      </c>
-      <c r="D101">
-        <v>138.9747085349312</v>
-      </c>
-      <c r="E101">
-        <v>92.44</v>
-      </c>
-      <c r="F101">
-        <v>154.44</v>
-      </c>
-      <c r="G101">
-        <v>17</v>
-      </c>
-      <c r="H101">
-        <v>94</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33.77777777777778</v>
-      </c>
-      <c r="K101">
-        <v>8.5</v>
-      </c>
-      <c r="L101">
-        <v>25.27777777777778</v>
-      </c>
-      <c r="M101">
-        <v>11.706552</v>
-      </c>
-      <c r="N101">
-        <v>13.57122577777778</v>
-      </c>
-      <c r="O101">
-        <v>2.985669671111111</v>
-      </c>
-      <c r="P101">
-        <v>10.58555610666667</v>
-      </c>
-      <c r="Q101">
-        <v>19.08555610666667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.617160868062324</v>
-      </c>
-      <c r="T101">
-        <v>66.51887066411732</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.05912400000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.159284627768943</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
